--- a/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
+++ b/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
@@ -86,7 +86,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -122,12 +122,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCDD2"/>
+        <fgColor rgb="FFC8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC8E6C9"/>
+        <fgColor rgb="FFFFCDD2"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,11 +138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE1F5FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -238,9 +233,6 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -250,16 +242,19 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1092,7 +1087,7 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>23 场已审核</t>
         </is>
@@ -1126,7 +1121,7 @@
           <t>启用</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>启用后缺少全量赔率会阻断正式生成</t>
         </is>
@@ -1221,7 +1216,7 @@
           <t>周日010</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>德国 vs 芬兰</t>
         </is>
@@ -2746,27 +2741,27 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>让 +1 → 客胜 覆盖13.7%</t>
+          <t>让 +1 → 主胜 覆盖69.8%</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>1-2 (7%)</t>
+          <t>2-1 (9%) | 备 1-0 (7%), 2-0 (7%)</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>客胜-客胜 (18%) | 另 平局-客胜 (11%)</t>
+          <t>主胜-主胜 (28%) | 另 平局-主胜 (14%)</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>主 35.3% / 平 28.3% / 客 36.3%</t>
+          <t>主 41.4% / 平 26.3% / 客 32.3%</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -2781,14 +2776,14 @@
 🔀 历史同情境(开→收盘口平稳):客队(热门)兑现 44%(982场)</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>🔴 低 (9.6) · ⚪ 慎选/观望 · EV -19.3%</t>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>🟠 偏低 (22.2) · ⚪ 慎选/观望 · EV 13.7% · 1.96/100</t>
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2798,7 @@
           <t>日职</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>清水鼓动 vs 横滨水手</t>
         </is>
@@ -2813,14 +2808,14 @@
           <t>05-31 13:00</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>让 -1 → 客胜 覆盖69.3%</t>
+          <t>让 -1 → 客胜 覆盖69.4%</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -2835,7 +2830,7 @@
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>主 31.8% / 平 26.9% / 客 41.4%</t>
+          <t>主 31.4% / 平 27.3% / 客 41.4%</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -2852,10 +2847,10 @@
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>🟠 偏低 (22.7) · ⚪ 慎选/观望 · EV -2.8%</t>
-        </is>
-      </c>
-      <c r="M4" s="14" t="inlineStr">
+          <t>🟠 偏低 (23) · ⚪ 慎选/观望 · EV -4.9%</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -2882,29 +2877,29 @@
           <t>05-31 18:25</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>让 -2 → 主胜 覆盖21.8%</t>
+          <t>让 -2 → 主胜 覆盖18.5%</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>2-0 (13%) | 备 1-0 (13%), 2-1 (9%)</t>
+          <t>1-0 (14%) | 备 2-0 (14%), 2-1 (9%)</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜 (45%) | 另 平局-主胜 (20%)</t>
+          <t>主胜-主胜 (42%) | 另 平局-主胜 (20%)</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 12.8% / 客 6.5%</t>
+          <t>主 76.2% / 平 17.8% / 客 6%</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -2917,9 +2912,9 @@
           <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
         </is>
       </c>
-      <c r="L5" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (100) · 🟢 建议下注 · EV -7.1%</t>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (91.7) · 🟢 建议下注 · EV -13.1%</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -2939,7 +2934,7 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>韦斯特罗斯 vs 哥德堡</t>
         </is>
@@ -2949,29 +2944,29 @@
           <t>05-31 20:00</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>主胜</t>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>客胜</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>让 -1 → 主胜 覆盖20.3%</t>
+          <t>让 -1 → 客胜 覆盖61.1%</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>1-0 (10%) | 备 2-1 (9%)</t>
+          <t>0-1 (8%)</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>主胜-主胜 (26%) | 另 平局-主胜 (15%)</t>
+          <t>客胜-客胜 (20%) | 另 平局-客胜 (12%)</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>主 41.4% / 平 26% / 客 32.7%</t>
+          <t>主 35.3% / 平 29% / 客 35.7%</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -2986,14 +2981,14 @@
 🔀 历史同情境(开→收盘口平稳):主队(热门)兑现 54%(1291场)</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>🟠 偏低 (21.8) · ⚪ 慎选/观望 · EV -2.4%</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>🔴 低 (8.5) · ⚪ 慎选/观望 · EV -9.3%</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3013,7 @@
           <t>05-31 20:00</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -3077,7 +3072,7 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>代格福什 vs 布鲁马波</t>
         </is>
@@ -3087,7 +3082,7 @@
           <t>05-31 20:00</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3129,7 +3124,7 @@
           <t>🟡 中等 (31.2) · ⚪ 慎选/观望 · EV -8.7%</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="M8" s="13" t="inlineStr">
         <is>
           <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3156,14 +3151,14 @@
           <t>05-31 21:00</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>让 -1 → 主胜 覆盖45.4%</t>
+          <t>让 -1 → 主胜 覆盖45.5%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -3178,7 +3173,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>主 57.9% / 平 22.7% / 客 19.3%</t>
+          <t>主 57.9% / 平 23% / 客 19%</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -3192,9 +3187,9 @@
 🔀 历史同情境(开→收盘口平稳):主队(热门)兑现 54%(887场)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (57.6) · 🟡 可选 · EV -7.9%</t>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (57.4) · 🟡 可选 · EV -10.8%</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -3214,7 +3209,7 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>捷克 vs 科索沃</t>
         </is>
@@ -3224,29 +3219,29 @@
           <t>05-31 22:00</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>让 -1 → 主胜 覆盖32.5%</t>
+          <t>让 -1 → 主胜 覆盖30.3%</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>1-0 (11%) | 备 2-0 (10%), 2-1 (10%)</t>
+          <t>1-0 (12%) | 备 2-0 (11%), 2-1 (10%)</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>主胜-主胜 (36%) | 另 平局-主胜 (18%)</t>
+          <t>主胜-主胜 (35%) | 另 平局-主胜 (18%)</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>主 57.9% / 平 24.7% / 客 17.4%</t>
+          <t>主 57.4% / 平 25.5% / 客 17.2%</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
@@ -3261,10 +3256,10 @@
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (55.9) · 🟡 可选 · EV -12.5%</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="inlineStr">
+          <t>🟢 较高 (54.2) · 🟡 可选 · EV -13.4%</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="inlineStr">
         <is>
           <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3291,29 +3286,29 @@
           <t>06-01 03:30</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>让 -1 → 主胜 覆盖21.9%</t>
+          <t>让 -1 → 主胜 覆盖20.5%</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2-1 (9%) | 备 1-0 (9%), 2-0 (8%)</t>
+          <t>1-0 (10%) | 备 2-1 (9%)</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜 (27%) | 另 平局-主胜 (15%)</t>
+          <t>主胜-主胜 (26%) | 另 平局-主胜 (15%)</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>主 35.3% / 平 30% / 客 34.7%</t>
+          <t>主 35.9% / 平 28.9% / 客 35.2%</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -3326,9 +3321,9 @@
           <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
         </is>
       </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>🔴 低 (8.6) · ⚪ 慎选/观望 · EV -14.1%</t>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>🔴 低 (9) · ⚪ 慎选/观望 · EV -12.7%</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -3448,7 +3443,7 @@
           <t>瑞士 对 约旦</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3458,14 +3453,14 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 13.6% / 客 5.7%</t>
+          <t>主 76.4% / 平 18.2% / 客 5.4%</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -3473,9 +3468,9 @@
           <t>公认 favorite</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (100)</t>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (97.6)</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
@@ -3493,12 +3488,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>德国 对 芬兰</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3508,14 +3503,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 13.4% / 客 5.9%</t>
+          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
@@ -3525,12 +3520,12 @@
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (100)</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>双选(概率差 67%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢 较高 (95.9)</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>双选(概率差 58%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3548,24 +3543,24 @@
           <t>美国 对 塞内加尔</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>主胜/平局/客胜</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>全选</t>
+          <t>双选</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>主 35.3% / 平 30% / 客 34.7%</t>
+          <t>主 35.9% / 平 28.9% / 客 35.2%</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -3573,14 +3568,14 @@
           <t>⚠ 爆冷有戏</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>🔴 低 (8.6)</t>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>🔴 低 (9)</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>⚠ 平局 ≥30% 且接近最高,三选全覆盖；爆冷:⚠ 爆冷有戏；经模型综合分析：国际赛，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日011 胜平负方向强制一致</t>
+          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:⚠ 爆冷有戏；经模型综合分析：国际赛，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日011 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3593,12 +3588,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>巴西 对 巴拿马</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3608,14 +3603,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 14% / 客 5.3%</t>
+          <t>主 76.5% / 平 18.5% / 客 5%</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -3625,12 +3620,12 @@
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (100)</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="inlineStr">
-        <is>
-          <t>双选(概率差 67%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢 较高 (95.8)</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>双选(概率差 58%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3643,7 @@
           <t>保加利亚 对 黑山</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -3658,7 +3653,7 @@
           <t>客胜/平局</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3693,12 +3688,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>挪威 对 瑞典</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3708,14 +3703,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>主 52.8% / 平 24.8% / 客 22.4%</t>
+          <t>主 52.3% / 平 25.5% / 客 22.2%</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -3725,12 +3720,12 @@
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (53.5)</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>双选(概率差 28%)；爆冷:⚠ 爆冷有戏；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢 较高 (52)</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:⚠ 爆冷有戏；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3743,7 @@
           <t>土耳其 对 北马其顿</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3758,14 +3753,14 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 13.4% / 客 5.9%</t>
+          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -3773,9 +3768,9 @@
           <t>公认 favorite</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (100)</t>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (97.6)</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -3793,12 +3788,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>奥地利 对 突尼斯</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3808,7 +3803,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -3828,7 +3823,7 @@
           <t>🟢 较高 (61.1)</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>✅ 胆码；爆冷:标准；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3848,7 +3843,7 @@
           <t>哥伦比亚 对 哥斯达黎加</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3858,14 +3853,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>主 72.5% / 平 17.9% / 客 9.6%</t>
+          <t>主 69.7% / 平 21% / 客 9.3%</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -3873,14 +3868,14 @@
           <t>公认 favorite</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (84.6)</t>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (77.2)</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>双选(概率差 55%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>双选(概率差 49%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3888,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>加拿大 对 乌兹别克斯坦</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3908,7 +3903,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3928,7 +3923,7 @@
           <t>🟢 较高 (60.3)</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:标准；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3948,7 +3943,7 @@
           <t>代格福什 对 布鲁马波卡纳</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3958,7 +3953,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3993,12 +3988,12 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>赫根 对 哈马比</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -4008,7 +4003,7 @@
           <t>客胜/主胜</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4028,7 +4023,7 @@
           <t>🟡 中等 (34.5)</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>双选(概率差 18%)；爆冷:⚠ 爆冷有戏；经模型综合分析：瑞超，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日005 胜平负方向强制一致</t>
         </is>
@@ -4048,7 +4043,7 @@
           <t>韦斯特罗斯 对 IFK 哥德堡</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -4058,7 +4053,7 @@
           <t>客胜/平局</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4093,12 +4088,12 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>AC 奥卢 对 雅罗</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4108,14 +4103,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>主 57.9% / 平 22.7% / 客 19.3%</t>
+          <t>主 57.9% / 平 23% / 客 19%</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -4125,10 +4120,10 @@
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (57.6)</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
+          <t>🟢 较高 (57.4)</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>双选(概率差 35%)；爆冷:标准；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日008 胜平负方向强制一致</t>
         </is>
@@ -4239,7 +4234,7 @@
           <t>土耳其 对 北马其顿</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4249,19 +4244,19 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 13.4% / 客 5.9%</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (100)</t>
+          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (97.6)</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -4279,39 +4274,39 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>德国 对 芬兰</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>瑞士 对 约旦</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
-          <t>双选</t>
+          <t>胆</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 13.4% / 客 5.9%</t>
+          <t>主 76.4% / 平 18.2% / 客 5.4%</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (100)</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>双选(差 67%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢 较高 (97.6)</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4326,37 +4321,37 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>瑞士 对 约旦</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+          <t>德国 对 芬兰</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>胆</t>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>双选</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 13.6% / 客 5.7%</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (100)</t>
+          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (95.9)</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4364,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>巴西 对 巴拿马</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4384,24 +4379,24 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>主 80.7% / 平 14% / 客 5.3%</t>
+          <t>主 76.5% / 平 18.5% / 客 5%</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (100)</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>双选(差 67%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢 较高 (95.8)</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4414,7 @@
           <t>哥伦比亚 对 哥斯达黎加</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4429,24 +4424,24 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>主 72.5% / 平 17.9% / 客 9.6%</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (84.6)</t>
+          <t>主 69.7% / 平 21% / 客 9.3%</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (77.2)</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>双选(差 55%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>双选(差 49%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4459,12 +4454,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>奥地利 对 突尼斯</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4474,7 +4469,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4489,7 +4484,7 @@
           <t>🟢 较高 (61.1)</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -4509,7 +4504,7 @@
           <t>加拿大 对 乌兹别克斯坦</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4519,7 +4514,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4529,7 +4524,7 @@
           <t>主 57.9% / 平 26.4% / 客 15.7%</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>🟢 较高 (60.3)</t>
         </is>
@@ -4549,12 +4544,12 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>AC 奥卢 对 雅罗</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4564,22 +4559,22 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>主 57.9% / 平 22.7% / 客 19.3%</t>
+          <t>主 57.9% / 平 23% / 客 19%</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (57.6)</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
+          <t>🟢 较高 (57.4)</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>⚠ 平局 ≥22% 强制覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日008 胜平负方向强制一致</t>
         </is>
@@ -4599,7 +4594,7 @@
           <t>挪威 对 瑞典</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4609,19 +4604,19 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>主 52.8% / 平 24.8% / 客 22.4%</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>🟢 较高 (53.5)</t>
+          <t>主 52.3% / 平 25.5% / 客 22.2%</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>🟢 较高 (52)</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -4633,13 +4628,13 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="17" t="inlineStr"/>
       <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="9" t="inlineStr"/>
       <c r="G12" s="9" t="inlineStr"/>
       <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -4653,7 +4648,7 @@
           <t>主胜 主胜 主胜 主胜 主胜 主胜 主胜 主胜 主胜</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr"/>
+      <c r="D13" s="15" t="inlineStr"/>
       <c r="E13" s="8" t="inlineStr"/>
       <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr"/>
@@ -4667,21 +4662,21 @@
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>独立估计 3.2%</t>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>独立估计 2.4%</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>相关性修正 6.5%</t>
+          <t>相关性修正 5%</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr"/>
       <c r="G14" s="9" t="inlineStr"/>
       <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -4692,10 +4687,10 @@
       <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>主胜 | 主胜/平局 | 主胜 | 主胜/平局 | 主胜/平局 | 主胜 | 主胜 | 主胜/平局 | 主胜</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
+          <t>主胜 | 主胜 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜 | 主胜 | 主胜/平局 | 主胜</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr"/>
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="8" t="inlineStr"/>
@@ -4709,7 +4704,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>从 14 场挑置信最高的 9 场单选;9 场全对即中任选9。联合命中率见 parlay(相关性修正后更诚实)。</t>
         </is>
@@ -4719,7 +4714,7 @@
       <c r="F16" s="9" t="inlineStr"/>
       <c r="G16" s="9" t="inlineStr"/>
       <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -5182,7 +5177,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN3" s="15" t="inlineStr">
+      <c r="AN3" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5218,7 +5213,7 @@
         </is>
       </c>
       <c r="AU3" s="8" t="n">
-        <v>100</v>
+        <v>97.58</v>
       </c>
       <c r="AV3" s="8" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN4" s="15" t="inlineStr">
+      <c r="AN4" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5398,7 +5393,7 @@
         </is>
       </c>
       <c r="AU4" s="9" t="n">
-        <v>100</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="AV4" s="9" t="inlineStr">
         <is>
@@ -5542,7 +5537,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN5" s="15" t="inlineStr">
+      <c r="AN5" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5578,7 +5573,7 @@
         </is>
       </c>
       <c r="AU5" s="8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="AV5" s="8" t="inlineStr">
         <is>
@@ -5722,7 +5717,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN6" s="15" t="inlineStr">
+      <c r="AN6" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5758,7 +5753,7 @@
         </is>
       </c>
       <c r="AU6" s="9" t="n">
-        <v>100</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="AV6" s="9" t="inlineStr">
         <is>
@@ -5902,7 +5897,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN7" s="12" t="inlineStr">
+      <c r="AN7" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -6082,7 +6077,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN8" s="15" t="inlineStr">
+      <c r="AN8" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6118,7 +6113,7 @@
         </is>
       </c>
       <c r="AU8" s="9" t="n">
-        <v>53.48</v>
+        <v>51.99</v>
       </c>
       <c r="AV8" s="9" t="inlineStr">
         <is>
@@ -6262,7 +6257,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN9" s="15" t="inlineStr">
+      <c r="AN9" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6298,7 +6293,7 @@
         </is>
       </c>
       <c r="AU9" s="8" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AV9" s="8" t="inlineStr">
         <is>
@@ -6442,7 +6437,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN10" s="15" t="inlineStr">
+      <c r="AN10" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6598,7 +6593,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN11" s="15" t="inlineStr">
+      <c r="AN11" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6610,7 +6605,7 @@
       </c>
       <c r="AP11" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AQ11" s="8" t="inlineStr">
@@ -6634,7 +6629,7 @@
         </is>
       </c>
       <c r="AU11" s="8" t="n">
-        <v>84.56</v>
+        <v>77.22</v>
       </c>
       <c r="AV11" s="8" t="inlineStr">
         <is>
@@ -6778,7 +6773,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN12" s="15" t="inlineStr">
+      <c r="AN12" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6958,7 +6953,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN13" s="15" t="inlineStr">
+      <c r="AN13" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -7138,7 +7133,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN14" s="12" t="inlineStr">
+      <c r="AN14" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -7318,7 +7313,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN15" s="12" t="inlineStr">
+      <c r="AN15" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -7498,7 +7493,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN16" s="15" t="inlineStr">
+      <c r="AN16" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -7534,7 +7529,7 @@
         </is>
       </c>
       <c r="AU16" s="9" t="n">
-        <v>57.64</v>
+        <v>57.36</v>
       </c>
       <c r="AV16" s="9" t="inlineStr">
         <is>
@@ -7580,7 +7575,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -7598,27 +7593,27 @@
         <v>2.22</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.13</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr"/>
@@ -7640,27 +7635,27 @@
         <v>5.2</v>
       </c>
       <c r="AE17" s="8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AG17" s="8" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AH17" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI17" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="AJ17" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.4</t>
         </is>
       </c>
       <c r="AK17" s="8" t="inlineStr">
@@ -7680,45 +7675,45 @@
       </c>
       <c r="AN17" s="12" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="AO17" s="8" t="inlineStr">
+        <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="AP17" s="8" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AQ17" s="8" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="AQ17" s="8" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="AR17" s="8" t="inlineStr">
         <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="AS17" s="8" t="inlineStr">
+        <is>
           <t>客胜-客胜</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
       <c r="AT17" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="AU17" s="8" t="n">
-        <v>9.57</v>
+        <v>22.17</v>
       </c>
       <c r="AV17" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7755,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
@@ -7778,27 +7773,27 @@
         <v>2.35</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="N18" s="9" t="n">
         <v>3.1</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
+          <t>+0.07</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Q18" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R18" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="S18" s="9" t="inlineStr"/>
@@ -7820,27 +7815,27 @@
         <v>1.35</v>
       </c>
       <c r="AE18" s="9" t="n">
-        <v>6.4</v>
+        <v>6.65</v>
       </c>
       <c r="AF18" s="9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG18" s="9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="AJ18" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AK18" s="9" t="inlineStr">
@@ -7858,7 +7853,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN18" s="12" t="inlineStr">
+      <c r="AN18" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -7894,7 +7889,7 @@
         </is>
       </c>
       <c r="AU18" s="9" t="n">
-        <v>22.65</v>
+        <v>23</v>
       </c>
       <c r="AV18" s="9" t="inlineStr">
         <is>
@@ -7940,7 +7935,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -7958,27 +7953,27 @@
         <v>11.5</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr"/>
@@ -8000,27 +7995,27 @@
         <v>2.05</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="AG19" s="8" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" s="8" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="AI19" s="8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ19" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.07</t>
         </is>
       </c>
       <c r="AK19" s="8" t="inlineStr">
@@ -8038,7 +8033,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN19" s="15" t="inlineStr">
+      <c r="AN19" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -8050,7 +8045,7 @@
       </c>
       <c r="AP19" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AQ19" s="8" t="inlineStr">
@@ -8074,7 +8069,7 @@
         </is>
       </c>
       <c r="AU19" s="8" t="n">
-        <v>100</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AV19" s="8" t="inlineStr">
         <is>
@@ -8120,7 +8115,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -8138,22 +8133,22 @@
         <v>2.54</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="O20" s="9" t="n">
         <v>2.54</v>
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.04</t>
         </is>
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="R20" s="9" t="inlineStr">
@@ -8218,47 +8213,47 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN20" s="15" t="inlineStr">
+      <c r="AN20" s="14" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="AO20" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="AO20" s="9" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="AP20" s="9" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="AQ20" s="9" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="AQ20" s="9" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="AR20" s="9" t="inlineStr">
         <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="AS20" s="9" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="AS20" s="9" t="inlineStr">
-        <is>
-          <t>客胜-客胜</t>
-        </is>
-      </c>
       <c r="AT20" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="AU20" s="9" t="n">
-        <v>21.83</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AV20" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8295,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -8398,7 +8393,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN21" s="12" t="inlineStr">
+      <c r="AN21" s="14" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -8480,7 +8475,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -8578,7 +8573,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN22" s="15" t="inlineStr">
+      <c r="AN22" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -8660,7 +8655,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -8678,27 +8673,27 @@
         <v>4.35</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="Q23" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr"/>
@@ -8720,27 +8715,27 @@
         <v>2.07</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AF23" s="8" t="n">
         <v>3.3</v>
       </c>
       <c r="AG23" s="8" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" s="8" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AI23" s="8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ23" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.08</t>
         </is>
       </c>
       <c r="AK23" s="8" t="inlineStr">
@@ -8758,7 +8753,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN23" s="15" t="inlineStr">
+      <c r="AN23" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -8794,7 +8789,7 @@
         </is>
       </c>
       <c r="AU23" s="8" t="n">
-        <v>57.64</v>
+        <v>57.36</v>
       </c>
       <c r="AV23" s="8" t="inlineStr">
         <is>
@@ -8840,7 +8835,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
@@ -8938,7 +8933,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN24" s="15" t="inlineStr">
+      <c r="AN24" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -8974,7 +8969,7 @@
         </is>
       </c>
       <c r="AU24" s="9" t="n">
-        <v>55.85</v>
+        <v>54.23</v>
       </c>
       <c r="AV24" s="9" t="inlineStr">
         <is>
@@ -9020,7 +9015,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -9118,7 +9113,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN25" s="15" t="inlineStr">
+      <c r="AN25" s="12" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -9130,12 +9125,12 @@
       </c>
       <c r="AP25" s="8" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AQ25" s="8" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="AR25" s="8" t="inlineStr">
@@ -9154,7 +9149,7 @@
         </is>
       </c>
       <c r="AU25" s="8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="AV25" s="8" t="inlineStr">
         <is>
@@ -9376,7 +9371,7 @@
         </is>
       </c>
       <c r="L3" s="8" t="n">
-        <v>100</v>
+        <v>97.58</v>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
@@ -9476,7 +9471,7 @@
         </is>
       </c>
       <c r="L4" s="9" t="n">
-        <v>100</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
@@ -9513,7 +9508,7 @@
           <t>常规｜赔率变化平稳；亚盘变化+0.5</t>
         </is>
       </c>
-      <c r="T4" s="14" t="inlineStr">
+      <c r="T4" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.5）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -9576,7 +9571,7 @@
         </is>
       </c>
       <c r="L5" s="8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
@@ -9676,7 +9671,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>100</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -9713,7 +9708,7 @@
           <t>常规｜赔率变化平稳；亚盘变化+0.5</t>
         </is>
       </c>
-      <c r="T6" s="14" t="inlineStr">
+      <c r="T6" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.5）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -9876,7 +9871,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>53.48</v>
+        <v>51.99</v>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
@@ -9913,7 +9908,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T8" s="14" t="inlineStr">
+      <c r="T8" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
@@ -9976,7 +9971,7 @@
         </is>
       </c>
       <c r="L9" s="8" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
@@ -10113,7 +10108,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T10" s="14" t="inlineStr">
+      <c r="T10" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
@@ -10167,7 +10162,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -10176,7 +10171,7 @@
         </is>
       </c>
       <c r="L11" s="8" t="n">
-        <v>84.56</v>
+        <v>77.22</v>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
@@ -10313,7 +10308,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T12" s="14" t="inlineStr">
+      <c r="T12" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
@@ -10513,7 +10508,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T14" s="14" t="inlineStr">
+      <c r="T14" s="13" t="inlineStr">
         <is>
           <t>主判断：客胜，防主胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.54）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -10676,7 +10671,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>57.64</v>
+        <v>57.36</v>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
@@ -10713,7 +10708,7 @@
           <t>常规｜赔率变化平稳；亚盘变化-0.25</t>
         </is>
       </c>
-      <c r="T16" s="14" t="inlineStr">
+      <c r="T16" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.86）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -10757,26 +10752,26 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
-        <v>9.57</v>
+        <v>22.17</v>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
@@ -10785,7 +10780,7 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>中高｜概率差过小</t>
+          <t>中高｜备选赔付不高，市场不排除</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr">
@@ -10815,7 +10810,7 @@
       </c>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>主判断：客胜，防主胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.42）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.42）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10871,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>22.65</v>
+        <v>23</v>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
@@ -10913,7 +10908,7 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T18" s="14" t="inlineStr">
+      <c r="T18" s="13" t="inlineStr">
         <is>
           <t>主判断：客胜，防主胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.42）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -10967,7 +10962,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -10976,7 +10971,7 @@
         </is>
       </c>
       <c r="L19" s="8" t="n">
-        <v>100</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
@@ -11057,26 +11052,26 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>21.83</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
@@ -11085,7 +11080,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>中高｜备选赔付不高，市场不排除</t>
+          <t>中高｜概率差过小</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
@@ -11113,9 +11108,9 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T20" s="14" t="inlineStr">
-        <is>
-          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.55）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+      <c r="T20" s="13" t="inlineStr">
+        <is>
+          <t>主判断：客胜，防主胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.55）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11308,7 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T22" s="14" t="inlineStr">
+      <c r="T22" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.65）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -11376,7 +11371,7 @@
         </is>
       </c>
       <c r="L23" s="8" t="n">
-        <v>57.64</v>
+        <v>57.36</v>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
@@ -11476,7 +11471,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>55.85</v>
+        <v>54.23</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
@@ -11513,7 +11508,7 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T24" s="14" t="inlineStr">
+      <c r="T24" s="13" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -11567,7 +11562,7 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -11576,7 +11571,7 @@
         </is>
       </c>
       <c r="L25" s="8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
@@ -12034,7 +12029,7 @@
       <c r="P4" s="9" t="inlineStr"/>
       <c r="Q4" s="9" t="inlineStr"/>
       <c r="R4" s="9" t="n">
-        <v>2.718</v>
+        <v>2.719</v>
       </c>
       <c r="S4" s="9" t="inlineStr">
         <is>
@@ -12679,7 +12674,7 @@
       <c r="P9" s="8" t="inlineStr"/>
       <c r="Q9" s="8" t="inlineStr"/>
       <c r="R9" s="8" t="n">
-        <v>2.719</v>
+        <v>2.718</v>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
@@ -12937,7 +12932,7 @@
       <c r="P11" s="8" t="inlineStr"/>
       <c r="Q11" s="8" t="inlineStr"/>
       <c r="R11" s="8" t="n">
-        <v>2.718</v>
+        <v>2.719</v>
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
@@ -13785,7 +13780,7 @@
       </c>
       <c r="AG17" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13964,7 @@
       <c r="P19" s="8" t="inlineStr"/>
       <c r="Q19" s="8" t="inlineStr"/>
       <c r="R19" s="8" t="n">
-        <v>2.718</v>
+        <v>2.719</v>
       </c>
       <c r="S19" s="8" t="inlineStr">
         <is>
@@ -14122,12 +14117,12 @@
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>均衡偏主动</t>
+          <t>均衡对抗/容错偏低</t>
         </is>
       </c>
       <c r="X20" s="9" t="inlineStr">
         <is>
-          <t>均衡偏主动</t>
+          <t>均衡对抗/容错偏低</t>
         </is>
       </c>
       <c r="Y20" s="9" t="inlineStr">
@@ -14172,7 +14167,7 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14609,7 @@
       <c r="P24" s="9" t="inlineStr"/>
       <c r="Q24" s="9" t="inlineStr"/>
       <c r="R24" s="9" t="n">
-        <v>2.719</v>
+        <v>2.718</v>
       </c>
       <c r="S24" s="9" t="inlineStr">
         <is>
@@ -15100,13 +15095,13 @@
         </is>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0.8074</v>
+        <v>0.764</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.1356</v>
+        <v>0.1821</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.057</v>
+        <v>0.0539</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>0.7876</v>
@@ -15118,17 +15113,17 @@
         <v>0.0629</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>0.6782</v>
+        <v>0.6682</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>0.1956</v>
+        <v>0.1962</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>0.1263</v>
+        <v>0.1357</v>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>1-0:13.5% / 2-0:13.1% / 2-1:9.5%</t>
+          <t>1-0:13.4% / 2-0:12.8% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U3" s="8" t="inlineStr">
@@ -15137,7 +15132,7 @@
         </is>
       </c>
       <c r="V3" s="8" t="n">
-        <v>100</v>
+        <v>97.58</v>
       </c>
       <c r="W3" s="8" t="inlineStr">
         <is>
@@ -15150,7 +15145,7 @@
         </is>
       </c>
       <c r="Y3" s="8" t="n">
-        <v>-0.0311</v>
+        <v>-0.0832</v>
       </c>
       <c r="Z3" s="8" t="n">
         <v>0</v>
@@ -15203,7 +15198,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>德国 对 芬兰</t>
         </is>
@@ -15239,13 +15234,13 @@
         </is>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.8074</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>0.1341</v>
+        <v>0.1811</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>0.0585</v>
+        <v>0.0553</v>
       </c>
       <c r="N4" s="9" t="n">
         <v>0.8398</v>
@@ -15257,17 +15252,17 @@
         <v>0.0487</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0.6819</v>
+        <v>0.668</v>
       </c>
       <c r="R4" s="9" t="n">
-        <v>0.1972</v>
+        <v>0.2046</v>
       </c>
       <c r="S4" s="9" t="n">
-        <v>0.121</v>
+        <v>0.1275</v>
       </c>
       <c r="T4" s="9" t="inlineStr">
         <is>
-          <t>2-0:13.4% / 1-0:13.4% / 2-1:9.4%</t>
+          <t>1-0:13.2% / 2-0:13.1% / 1-1:9.6%</t>
         </is>
       </c>
       <c r="U4" s="9" t="inlineStr">
@@ -15276,7 +15271,7 @@
         </is>
       </c>
       <c r="V4" s="9" t="n">
-        <v>100</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -15289,7 +15284,7 @@
         </is>
       </c>
       <c r="Y4" s="9" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1448</v>
       </c>
       <c r="Z4" s="9" t="n">
         <v>0</v>
@@ -15378,13 +15373,13 @@
         </is>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.3533</v>
+        <v>0.3592</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.3002</v>
+        <v>0.2886</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.3465</v>
+        <v>0.3523</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>0.3624</v>
@@ -15415,7 +15410,7 @@
         </is>
       </c>
       <c r="V5" s="8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="W5" s="8" t="inlineStr">
         <is>
@@ -15428,7 +15423,7 @@
         </is>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>-0.1097</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="Z5" s="8" t="n">
         <v>0</v>
@@ -15481,7 +15476,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>巴西 对 巴拿马</t>
         </is>
@@ -15517,13 +15512,13 @@
         </is>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.8074</v>
+        <v>0.765</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.1395</v>
+        <v>0.1847</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.0531</v>
+        <v>0.0503</v>
       </c>
       <c r="N6" s="9" t="n">
         <v>0.8421</v>
@@ -15535,17 +15530,17 @@
         <v>0.0435</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0.6884</v>
+        <v>0.6723</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>0.1925</v>
+        <v>0.1988</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0.1192</v>
+        <v>0.129</v>
       </c>
       <c r="T6" s="9" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:13.3% / 3-0:9.4%</t>
+          <t>2-0:13.2% / 1-0:13% / 1-1:9.3%</t>
         </is>
       </c>
       <c r="U6" s="9" t="inlineStr">
@@ -15554,7 +15549,7 @@
         </is>
       </c>
       <c r="V6" s="9" t="n">
-        <v>100</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -15567,7 +15562,7 @@
         </is>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>-0.1038</v>
+        <v>-0.1508</v>
       </c>
       <c r="Z6" s="9" t="n">
         <v>0</v>
@@ -15759,7 +15754,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>挪威 对 瑞典</t>
         </is>
@@ -15795,13 +15790,13 @@
         </is>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.5281</v>
+        <v>0.523</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.2475</v>
+        <v>0.2548</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.2244</v>
+        <v>0.2222</v>
       </c>
       <c r="N8" s="9" t="n">
         <v>0.4907</v>
@@ -15813,17 +15808,17 @@
         <v>0.2422</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>0.5343</v>
+        <v>0.5336</v>
       </c>
       <c r="R8" s="9" t="n">
         <v>0.2425</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>0.2233</v>
+        <v>0.224</v>
       </c>
       <c r="T8" s="9" t="inlineStr">
         <is>
-          <t>1-1:11.6% / 1-0:11.4% / 2-0:9.7%</t>
+          <t>1-1:11.6% / 1-0:11.4% / 2-0:9.6%</t>
         </is>
       </c>
       <c r="U8" s="9" t="inlineStr">
@@ -15832,7 +15827,7 @@
         </is>
       </c>
       <c r="V8" s="9" t="n">
-        <v>53.48</v>
+        <v>51.99</v>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -15845,7 +15840,7 @@
         </is>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>-0.0177</v>
+        <v>-0.0272</v>
       </c>
       <c r="Z8" s="9" t="n">
         <v>0</v>
@@ -15934,13 +15929,13 @@
         </is>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.8074</v>
+        <v>0.7635</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.134</v>
+        <v>0.181</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.0586</v>
+        <v>0.0554</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>0.7586000000000001</v>
@@ -15952,17 +15947,17 @@
         <v>0.0735</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.6801</v>
+        <v>0.6684</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>0.1966</v>
+        <v>0.2017</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>0.1233</v>
+        <v>0.1299</v>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>1-0:13.6% / 2-0:13.3% / 1-1:9.4%</t>
+          <t>1-0:13.4% / 2-0:13% / 1-1:9.6%</t>
         </is>
       </c>
       <c r="U9" s="8" t="inlineStr">
@@ -15971,7 +15966,7 @@
         </is>
       </c>
       <c r="V9" s="8" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="W9" s="8" t="inlineStr">
         <is>
@@ -15984,10 +15979,10 @@
         </is>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>0.0012</v>
+        <v>-0.0533</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="8" t="n">
         <v>0.6205000000000001</v>
@@ -16037,7 +16032,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>奥地利 对 突尼斯</t>
         </is>
@@ -16193,7 +16188,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -16212,13 +16207,13 @@
         </is>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.725</v>
+        <v>0.6972</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.1788</v>
+        <v>0.2103</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0925</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>0.7082000000000001</v>
@@ -16230,17 +16225,17 @@
         <v>0.1021</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>0.6446</v>
+        <v>0.636</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>0.2149</v>
+        <v>0.2175</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>0.1406</v>
+        <v>0.1466</v>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>1-0:13.1% / 2-0:12.4% / 1-1:10.3%</t>
+          <t>1-0:12.9% / 2-0:12.2% / 1-1:10.3%</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
@@ -16249,7 +16244,7 @@
         </is>
       </c>
       <c r="V11" s="8" t="n">
-        <v>84.56</v>
+        <v>77.22</v>
       </c>
       <c r="W11" s="8" t="inlineStr">
         <is>
@@ -16262,7 +16257,7 @@
         </is>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>-0.0502</v>
+        <v>-0.0867</v>
       </c>
       <c r="Z11" s="8" t="n">
         <v>0</v>
@@ -16315,7 +16310,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>加拿大 对 乌兹别克斯坦</t>
         </is>
@@ -16593,7 +16588,7 @@
           <t>瑞超</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>赫根 对 哈马比</t>
         </is>
@@ -16871,7 +16866,7 @@
           <t>芬超</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>AC 奥卢 对 雅罗</t>
         </is>
@@ -16910,10 +16905,10 @@
         <v>0.5793</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.2273</v>
+        <v>0.2304</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>0.1934</v>
+        <v>0.1903</v>
       </c>
       <c r="N16" s="9" t="n">
         <v>0.5848</v>
@@ -16944,7 +16939,7 @@
         </is>
       </c>
       <c r="V16" s="9" t="n">
-        <v>57.64</v>
+        <v>57.36</v>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -17017,64 +17012,64 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
           <t>客胜-客胜</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
       <c r="K17" s="8" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="S17" s="8" t="n">
         <v>0.3533</v>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>0.2833</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>0.3634</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>0.3678</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>0.2769</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>0.3373</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>0.2807</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>0.3821</v>
-      </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>1-1:13.1% / 0-1:10.9% / 1-0:10.1%</t>
+          <t>1-1:13.2% / 1-0:10.7% / 0-1:10.5%</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
@@ -17083,7 +17078,7 @@
         </is>
       </c>
       <c r="V17" s="8" t="n">
-        <v>9.57</v>
+        <v>22.17</v>
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
@@ -17096,37 +17091,37 @@
         </is>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>-0.1933</v>
+        <v>0.1374</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>0.3694</v>
+        <v>0.3737</v>
       </c>
       <c r="AB17" s="8" t="n">
-        <v>0.2489</v>
+        <v>0.2502</v>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>0.3817</v>
+        <v>0.3761</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>5</v>
       </c>
       <c r="AE17" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="AG17" s="8" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="AH17" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI17" s="8" t="inlineStr"/>
@@ -17149,7 +17144,7 @@
           <t>日职</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>清水鼓动 对 横滨水手</t>
         </is>
@@ -17185,31 +17180,31 @@
         </is>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.3178</v>
+        <v>0.3139</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.2686</v>
+        <v>0.2725</v>
       </c>
       <c r="M18" s="9" t="n">
         <v>0.4136</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>0.3378</v>
+        <v>0.3292</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>0.2855</v>
+        <v>0.2857</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.3766</v>
+        <v>0.3851</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>0.3203</v>
+        <v>0.3185</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0.2718</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0.408</v>
+        <v>0.4098</v>
       </c>
       <c r="T18" s="9" t="inlineStr">
         <is>
@@ -17222,7 +17217,7 @@
         </is>
       </c>
       <c r="V18" s="9" t="n">
-        <v>22.65</v>
+        <v>23</v>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -17235,19 +17230,19 @@
         </is>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>-0.028</v>
+        <v>-0.0487</v>
       </c>
       <c r="Z18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>0.3923</v>
+        <v>0.3891</v>
       </c>
       <c r="AB18" s="9" t="n">
-        <v>0.236</v>
+        <v>0.2361</v>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>0.3717</v>
+        <v>0.3748</v>
       </c>
       <c r="AD18" s="9" t="n">
         <v>4</v>
@@ -17258,14 +17253,14 @@
         </is>
       </c>
       <c r="AF18" s="9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" s="9" t="n">
         <v>2.35</v>
       </c>
       <c r="AH18" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI18" s="9" t="inlineStr"/>
@@ -17305,7 +17300,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -17324,35 +17319,35 @@
         </is>
       </c>
       <c r="K19" s="8" t="n">
-        <v>0.8074</v>
+        <v>0.7622</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.128</v>
+        <v>0.1776</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.0646</v>
+        <v>0.0602</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>0.7703</v>
+        <v>0.7772</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>0.1527</v>
+        <v>0.1489</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>0.077</v>
+        <v>0.0738</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>0.6811</v>
+        <v>0.6685</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>0.1979</v>
+        <v>0.2021</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>0.1211</v>
+        <v>0.1295</v>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:13.1% / 1-1:9.4%</t>
+          <t>1-0:13% / 2-0:13% / 1-1:9.7%</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -17361,7 +17356,7 @@
         </is>
       </c>
       <c r="V19" s="8" t="n">
-        <v>100</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="W19" s="8" t="inlineStr">
         <is>
@@ -17374,19 +17369,19 @@
         </is>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1311</v>
       </c>
       <c r="Z19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="n">
-        <v>0.5548</v>
+        <v>0.5575</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>0.1925</v>
+        <v>0.191</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>0.2527</v>
+        <v>0.2515</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>4</v>
@@ -17397,14 +17392,14 @@
         </is>
       </c>
       <c r="AF19" s="8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AG19" s="8" t="n">
         <v>1.15</v>
       </c>
       <c r="AH19" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI19" s="8" t="inlineStr"/>
@@ -17427,71 +17422,71 @@
           <t>瑞超</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>韦斯特罗斯 对 哥德堡</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>客胜-客胜</t>
-        </is>
-      </c>
       <c r="K20" s="9" t="n">
-        <v>0.4136</v>
+        <v>0.3533</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.2595</v>
+        <v>0.2897</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>0.3269</v>
+        <v>0.357</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>0.375</v>
+        <v>0.3688</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>0.2766</v>
+        <v>0.2828</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0.3484</v>
+        <v>0.3485</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>0.4283</v>
+        <v>0.3962</v>
       </c>
       <c r="R20" s="9" t="n">
-        <v>0.2675</v>
+        <v>0.2678</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0.3043</v>
+        <v>0.3361</v>
       </c>
       <c r="T20" s="9" t="inlineStr">
         <is>
-          <t>1-1:12.5% / 1-0:11% / 2-1:8.9%</t>
+          <t>1-1:12.5% / 1-0:10.1% / 0-1:9.3%</t>
         </is>
       </c>
       <c r="U20" s="9" t="inlineStr">
@@ -17500,7 +17495,7 @@
         </is>
       </c>
       <c r="V20" s="9" t="n">
-        <v>21.83</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -17513,37 +17508,37 @@
         </is>
       </c>
       <c r="Y20" s="9" t="n">
-        <v>-0.0239</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="Z20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AA20" s="9" t="n">
-        <v>0.4057</v>
+        <v>0.4033</v>
       </c>
       <c r="AB20" s="9" t="n">
-        <v>0.2392</v>
+        <v>0.2415</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>0.3551</v>
+        <v>0.3552</v>
       </c>
       <c r="AD20" s="9" t="n">
         <v>4</v>
       </c>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AF20" s="9" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="AG20" s="9" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="AH20" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI20" s="9" t="inlineStr"/>
@@ -17682,7 +17677,7 @@
       </c>
       <c r="AH21" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI21" s="8" t="inlineStr"/>
@@ -17705,7 +17700,7 @@
           <t>瑞超</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>代格福什 对 布鲁马波</t>
         </is>
@@ -17821,7 +17816,7 @@
       </c>
       <c r="AH22" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI22" s="9" t="inlineStr"/>
@@ -17883,28 +17878,28 @@
         <v>0.5793</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.2273</v>
+        <v>0.2304</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.1934</v>
+        <v>0.1903</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5747</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>0.2394</v>
+        <v>0.2329</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>0.2036</v>
+        <v>0.1924</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>0.1846</v>
+        <v>0.1858</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>0.1134</v>
+        <v>0.1123</v>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
@@ -17917,7 +17912,7 @@
         </is>
       </c>
       <c r="V23" s="8" t="n">
-        <v>57.64</v>
+        <v>57.36</v>
       </c>
       <c r="W23" s="8" t="inlineStr">
         <is>
@@ -17930,19 +17925,19 @@
         </is>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>-0.0789</v>
+        <v>-0.1079</v>
       </c>
       <c r="Z23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="n">
-        <v>0.4743</v>
+        <v>0.481</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>0.2252</v>
+        <v>0.2227</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>0.3005</v>
+        <v>0.2963</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>4</v>
@@ -17953,14 +17948,14 @@
         </is>
       </c>
       <c r="AF23" s="8" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG23" s="8" t="n">
         <v>1.59</v>
       </c>
       <c r="AH23" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI23" s="8" t="inlineStr"/>
@@ -17983,7 +17978,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>捷克 对 科索沃</t>
         </is>
@@ -18019,13 +18014,13 @@
         </is>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.5793</v>
+        <v>0.5735</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.2472</v>
+        <v>0.2547</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>0.1735</v>
+        <v>0.1718</v>
       </c>
       <c r="N24" s="9" t="n">
         <v>0.5868</v>
@@ -18037,17 +18032,17 @@
         <v>0.1704</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>0.5727</v>
+        <v>0.5707</v>
       </c>
       <c r="R24" s="9" t="n">
-        <v>0.232</v>
+        <v>0.2328</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>0.1954</v>
+        <v>0.1966</v>
       </c>
       <c r="T24" s="9" t="inlineStr">
         <is>
-          <t>1-0:11.6% / 1-1:10.9% / 2-0:10.8%</t>
+          <t>1-0:11.6% / 1-1:10.9% / 2-0:10.7%</t>
         </is>
       </c>
       <c r="U24" s="9" t="inlineStr">
@@ -18056,7 +18051,7 @@
         </is>
       </c>
       <c r="V24" s="9" t="n">
-        <v>55.85</v>
+        <v>54.23</v>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -18069,7 +18064,7 @@
         </is>
       </c>
       <c r="Y24" s="9" t="n">
-        <v>-0.1253</v>
+        <v>-0.134</v>
       </c>
       <c r="Z24" s="9" t="n">
         <v>0</v>
@@ -18099,7 +18094,7 @@
       </c>
       <c r="AH24" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI24" s="9" t="inlineStr"/>
@@ -18139,12 +18134,12 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -18158,13 +18153,13 @@
         </is>
       </c>
       <c r="K25" s="8" t="n">
-        <v>0.3533</v>
+        <v>0.3592</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.3002</v>
+        <v>0.2886</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.3465</v>
+        <v>0.3523</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>0.3643</v>
@@ -18179,10 +18174,10 @@
         <v>0.4389</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>0.2554</v>
+        <v>0.2555</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>0.3058</v>
+        <v>0.3057</v>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
@@ -18195,7 +18190,7 @@
         </is>
       </c>
       <c r="V25" s="8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
@@ -18208,7 +18203,7 @@
         </is>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>-0.1415</v>
+        <v>-0.1271</v>
       </c>
       <c r="Z25" s="8" t="n">
         <v>0</v>
@@ -18238,7 +18233,7 @@
       </c>
       <c r="AH25" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T11:54:50+08:00</t>
+          <t>2026-05-31T12:15:15+08:00</t>
         </is>
       </c>
       <c r="AI25" s="8" t="inlineStr"/>

--- a/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
+++ b/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜 (28%) | 另 平局-主胜 (14%)</t>
+          <t>主胜-主胜 (25%) | 另 平局-主胜 (15%)</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>客胜-客胜 (24%) | 另 平局-客胜 (15%)</t>
+          <t>客胜-客胜 (22%) | 另 平局-客胜 (15%)</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜 (42%) | 另 平局-主胜 (20%)</t>
+          <t>主胜-主胜 (40%) | 另 平局-主胜 (21%)</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>客胜-客胜 (20%) | 另 平局-客胜 (12%)</t>
+          <t>客胜-客胜 (17%) | 另 平局-客胜 (12%)</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>客胜-客胜 (34%) | 另 平局-客胜 (18%)</t>
+          <t>客胜-客胜 (31%) | 另 平局-客胜 (18%)</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>主胜-主胜 (30%) | 另 平局-主胜 (16%)</t>
+          <t>主胜-主胜 (28%) | 另 平局-主胜 (17%)</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜 (47%) | 另 平局-主胜 (20%)</t>
+          <t>主胜-主胜 (45%) | 另 平局-主胜 (21%)</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>主胜-主胜 (35%) | 另 平局-主胜 (18%)</t>
+          <t>主胜-主胜 (33%) | 另 平局-主胜 (19%)</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜 (26%) | 另 平局-主胜 (15%)</t>
+          <t>主胜-主胜 (24%) | 另 平局-主胜 (15%)</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">

--- a/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
+++ b/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据缺失·未预测" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全面审计'!$A$2:$C$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'出表自检'!$A$2:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全面审计'!$A$2:$C$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'出表自检'!$A$2:$I$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'神选·竞彩'!$A$2:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'神选·14场'!$A$2:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'神选·任选9'!$A$2:$I$18</definedName>
@@ -122,12 +122,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC8E6C9"/>
+        <fgColor rgb="FFFFCDD2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCDD2"/>
+        <fgColor rgb="FFC8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +233,9 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -242,13 +245,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -727,7 +724,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>blocker 0 / warning 9</t>
+          <t>blocker 0 / warning 6</t>
         </is>
       </c>
     </row>
@@ -935,7 +932,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>逐场自检:[韦斯特罗斯 vs 哥德堡] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>逐场自检:[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
@@ -948,7 +945,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>逐场自检:[赫根 vs 哈马比] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>逐场自检:[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
@@ -961,61 +958,22 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>逐场自检:[代格福什 vs 布鲁马波] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="8" t="inlineStr"/>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>逐场自检:[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="9" t="inlineStr"/>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>逐场自检:[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="8" t="inlineStr"/>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
           <t>逐场自检:[美国 vs 塞内加尔] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C31"/>
+  <autoFilter ref="A2:C28"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1087,7 +1045,7 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>23 场已审核</t>
         </is>
@@ -1121,7 +1079,7 @@
           <t>启用</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>启用后缺少全量赔率会阻断正式生成</t>
         </is>
@@ -1216,7 +1174,7 @@
           <t>周日010</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>德国 vs 芬兰</t>
         </is>
@@ -1277,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1311,12 +1269,12 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>DC真跑 14 · 仅赔率 9 · 融合fire 0</t>
+          <t>DC真跑 17 · 仅赔率 6 · 融合fire 0</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>拦截 0 · 提示 9</t>
+          <t>拦截 0 · 提示 6</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -2209,7 +2167,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>⚠仅赔率</t>
+          <t>✓DC</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -2256,7 +2214,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>⚠仅赔率</t>
+          <t>✓DC</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -2303,7 +2261,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>⚠仅赔率</t>
+          <t>✓DC</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -2516,7 +2474,7 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>[韦斯特罗斯 vs 哥德堡] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr"/>
@@ -2531,7 +2489,7 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>[赫根 vs 哈马比] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr"/>
@@ -2546,7 +2504,7 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>[代格福什 vs 布鲁马波] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>[美国 vs 塞内加尔] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr"/>
@@ -2558,63 +2516,18 @@
       <c r="H33" s="8" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr"/>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr"/>
-      <c r="C34" s="9" t="inlineStr"/>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
-      <c r="I34" s="9" t="inlineStr"/>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="8" t="inlineStr"/>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>[美国 vs 塞内加尔] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr"/>
-      <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="9" t="inlineStr"/>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr"/>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I38"/>
+  <autoFilter ref="A2:I35"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A35:I35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2741,27 +2654,27 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>让 +1 → 主胜 覆盖69.8%</t>
+          <t>让 +1 → 客胜 覆盖15.9%</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>2-1 (9%) | 备 1-0 (7%), 2-0 (7%)</t>
+          <t>0-1 (9%)</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜 (25%) | 另 平局-主胜 (15%)</t>
+          <t>客胜-客胜 (19%) | 另 平局-客胜 (13%)</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>主 41.4% / 平 26.3% / 客 32.3%</t>
+          <t>主 34.6% / 平 30.1% / 客 35.3%</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -2776,14 +2689,14 @@
 🔀 历史同情境(开→收盘口平稳):客队(热门)兑现 44%(982场)</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>🟠 偏低 (22.2) · ⚪ 慎选/观望 · EV 13.7% · 1.96/100</t>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>🔴 低 (8.6) · ⚪ 慎选/观望 · EV -17.0%</t>
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2711,7 @@
           <t>日职</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>清水鼓动 vs 横滨水手</t>
         </is>
@@ -2808,7 +2721,7 @@
           <t>05-31 13:00</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -2850,7 +2763,7 @@
           <t>🟠 偏低 (23) · ⚪ 慎选/观望 · EV -4.9%</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -2877,7 +2790,7 @@
           <t>05-31 18:25</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -2912,7 +2825,7 @@
           <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (91.7) · 🟢 建议下注 · EV -13.1%</t>
         </is>
@@ -2934,7 +2847,7 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>韦斯特罗斯 vs 哥德堡</t>
         </is>
@@ -2944,29 +2857,29 @@
           <t>05-31 20:00</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>客胜</t>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>让 -1 → 客胜 覆盖61.1%</t>
+          <t>让 -1 → 主胜 覆盖43.3%</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>0-1 (8%)</t>
+          <t>2-0 (11%) | 备 2-1 (10%), 1-0 (10%)</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>客胜-客胜 (17%) | 另 平局-客胜 (12%)</t>
+          <t>主胜-主胜 (43%) | 另 平局-主胜 (20%)</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>主 35.3% / 平 29% / 客 35.7%</t>
+          <t>主 50% / 平 24.2% / 客 25.8%</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -2981,14 +2894,14 @@
 🔀 历史同情境(开→收盘口平稳):主队(热门)兑现 54%(1291场)</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>🔴 低 (8.5) · ⚪ 慎选/观望 · EV -9.3%</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>🟢 较高 (42.1) · 🟡 可选 · EV 20.0% · 2/100</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3013,29 +2926,29 @@
           <t>05-31 20:00</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>让 +1 → 客胜 覆盖28.9%</t>
+          <t>让 +1 → 客胜 覆盖26.7%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>0-1 (12%) | 备 0-2 (10%), 1-2 (10%)</t>
+          <t>1-2 (9%) | 备 0-1 (7%), 0-2 (7%)</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>客胜-客胜 (31%) | 另 平局-客胜 (18%)</t>
+          <t>客胜-客胜 (28%) | 另 平局-客胜 (16%)</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>主 29.3% / 平 23.5% / 客 47.3%</t>
+          <t>主 28.7% / 平 24% / 客 47.3%</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -3052,7 +2965,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>🟡 中等 (34.5) · ⚪ 慎选/观望 · EV -4.5%</t>
+          <t>🟡 中等 (35) · ⚪ 慎选/观望 · EV -4.5%</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -3072,7 +2985,7 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>代格福什 vs 布鲁马波</t>
         </is>
@@ -3082,29 +2995,29 @@
           <t>05-31 20:00</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>让 -1 → 主胜 覆盖25.4%</t>
+          <t>让 -1 → 主胜 覆盖16.8%</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>1-0 (10%) | 备 2-1 (9%), 2-0 (9%)</t>
+          <t>2-1 (8%) | 备 1-0 (7%)</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>主胜-主胜 (28%) | 另 平局-主胜 (17%)</t>
+          <t>主胜-主胜 (19%) | 另 平局-主胜 (13%)</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>主 44.5% / 平 27.4% / 客 28%</t>
+          <t>主 41.4% / 平 27.1% / 客 31.5%</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -3121,10 +3034,10 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>🟡 中等 (31.2) · ⚪ 慎选/观望 · EV -8.7%</t>
-        </is>
-      </c>
-      <c r="M8" s="13" t="inlineStr">
+          <t>🟠 偏低 (23.1) · ⚪ 慎选/观望 · EV -15.0%</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
         <is>
           <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3151,7 +3064,7 @@
           <t>05-31 21:00</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3187,7 +3100,7 @@
 🔀 历史同情境(开→收盘口平稳):主队(热门)兑现 54%(887场)</t>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (57.4) · 🟡 可选 · EV -10.8%</t>
         </is>
@@ -3209,7 +3122,7 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>捷克 vs 科索沃</t>
         </is>
@@ -3219,7 +3132,7 @@
           <t>05-31 22:00</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3259,7 +3172,7 @@
           <t>🟢 较高 (54.2) · 🟡 可选 · EV -13.4%</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr">
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3286,7 +3199,7 @@
           <t>06-01 03:30</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3321,7 +3234,7 @@
           <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>🔴 低 (9) · ⚪ 慎选/观望 · EV -12.7%</t>
         </is>
@@ -3443,7 +3356,7 @@
           <t>瑞士 对 约旦</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3453,7 +3366,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -3468,7 +3381,7 @@
           <t>公认 favorite</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (97.6)</t>
         </is>
@@ -3488,12 +3401,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>德国 对 芬兰</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3503,7 +3416,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3523,7 +3436,7 @@
           <t>🟢 较高 (95.9)</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>双选(概率差 58%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3543,7 +3456,7 @@
           <t>美国 对 塞内加尔</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3553,7 +3466,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3568,7 +3481,7 @@
           <t>⚠ 爆冷有戏</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>🔴 低 (9)</t>
         </is>
@@ -3588,12 +3501,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>巴西 对 巴拿马</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3603,7 +3516,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3623,7 +3536,7 @@
           <t>🟢 较高 (95.8)</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>双选(概率差 58%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3643,7 +3556,7 @@
           <t>保加利亚 对 黑山</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -3653,7 +3566,7 @@
           <t>客胜/平局</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3688,12 +3601,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>挪威 对 瑞典</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3703,7 +3616,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3723,7 +3636,7 @@
           <t>🟢 较高 (52)</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:⚠ 爆冷有戏；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3743,7 +3656,7 @@
           <t>土耳其 对 北马其顿</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3753,7 +3666,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -3768,7 +3681,7 @@
           <t>公认 favorite</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (97.6)</t>
         </is>
@@ -3788,12 +3701,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>奥地利 对 突尼斯</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3803,7 +3716,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -3823,7 +3736,7 @@
           <t>🟢 较高 (61.1)</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>✅ 胆码；爆冷:标准；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3843,7 +3756,7 @@
           <t>哥伦比亚 对 哥斯达黎加</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3853,7 +3766,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3868,7 +3781,7 @@
           <t>公认 favorite</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (77.2)</t>
         </is>
@@ -3888,12 +3801,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>加拿大 对 乌兹别克斯坦</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3903,7 +3816,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3923,7 +3836,7 @@
           <t>🟢 较高 (60.3)</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:标准；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -3943,7 +3856,7 @@
           <t>代格福什 对 布鲁马波卡纳</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -3953,14 +3866,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>主 41.4% / 平 28.2% / 客 30.3%</t>
+          <t>主 41.4% / 平 27.1% / 客 31.5%</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -3970,12 +3883,12 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>🟡 中等 (30)</t>
+          <t>🟠 偏低 (23.1)</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:⚠ 爆冷有戏；经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:⚠ 爆冷有戏；经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日006 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3988,12 +3901,12 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>赫根 对 哈马比</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -4003,14 +3916,14 @@
           <t>客胜/主胜</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>主 29.3% / 平 23.5% / 客 47.3%</t>
+          <t>主 28.7% / 平 24% / 客 47.3%</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -4020,12 +3933,12 @@
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>🟡 中等 (34.5)</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>双选(概率差 18%)；爆冷:⚠ 爆冷有戏；经模型综合分析：瑞超，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日005 胜平负方向强制一致</t>
+          <t>🟡 中等 (35)</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>双选(概率差 19%)；爆冷:⚠ 爆冷有戏；经模型综合分析：瑞超，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日005 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4043,7 +3956,7 @@
           <t>韦斯特罗斯 对 IFK 哥德堡</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -4053,7 +3966,7 @@
           <t>客胜/平局</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4088,12 +4001,12 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>AC 奥卢 对 雅罗</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4103,7 +4016,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4123,7 +4036,7 @@
           <t>🟢 较高 (57.4)</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>双选(概率差 35%)；爆冷:标准；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日008 胜平负方向强制一致</t>
         </is>
@@ -4234,7 +4147,7 @@
           <t>土耳其 对 北马其顿</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4244,7 +4157,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4254,7 +4167,7 @@
           <t>主 76.4% / 平 18.1% / 客 5.5%</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (97.6)</t>
         </is>
@@ -4274,12 +4187,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>瑞士 对 约旦</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4289,7 +4202,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4304,7 +4217,7 @@
           <t>🟢 较高 (97.6)</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -4324,7 +4237,7 @@
           <t>德国 对 芬兰</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4334,7 +4247,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4344,7 +4257,7 @@
           <t>主 76.4% / 平 18.1% / 客 5.5%</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (95.9)</t>
         </is>
@@ -4364,12 +4277,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>巴西 对 巴拿马</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4379,7 +4292,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4394,7 +4307,7 @@
           <t>🟢 较高 (95.8)</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -4414,7 +4327,7 @@
           <t>哥伦比亚 对 哥斯达黎加</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4424,7 +4337,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4434,7 +4347,7 @@
           <t>主 69.7% / 平 21% / 客 9.3%</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (77.2)</t>
         </is>
@@ -4454,12 +4367,12 @@
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>奥地利 对 突尼斯</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4469,7 +4382,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4484,7 +4397,7 @@
           <t>🟢 较高 (61.1)</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
@@ -4504,7 +4417,7 @@
           <t>加拿大 对 乌兹别克斯坦</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4514,7 +4427,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4524,7 +4437,7 @@
           <t>主 57.9% / 平 26.4% / 客 15.7%</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (60.3)</t>
         </is>
@@ -4544,12 +4457,12 @@
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>AC 奥卢 对 雅罗</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4559,7 +4472,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4574,7 +4487,7 @@
           <t>🟢 较高 (57.4)</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>⚠ 平局 ≥22% 强制覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日008 胜平负方向强制一致</t>
         </is>
@@ -4594,7 +4507,7 @@
           <t>挪威 对 瑞典</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -4604,7 +4517,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4614,7 +4527,7 @@
           <t>主 52.3% / 平 25.5% / 客 22.2%</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>🟢 较高 (52)</t>
         </is>
@@ -4628,13 +4541,13 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="13" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr"/>
       <c r="D12" s="17" t="inlineStr"/>
       <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="9" t="inlineStr"/>
       <c r="G12" s="9" t="inlineStr"/>
       <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -4648,7 +4561,7 @@
           <t>主胜 主胜 主胜 主胜 主胜 主胜 主胜 主胜 主胜</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr"/>
+      <c r="D13" s="16" t="inlineStr"/>
       <c r="E13" s="8" t="inlineStr"/>
       <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr"/>
@@ -4662,7 +4575,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>独立估计 2.4%</t>
         </is>
@@ -4676,7 +4589,7 @@
       <c r="F14" s="9" t="inlineStr"/>
       <c r="G14" s="9" t="inlineStr"/>
       <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -4690,7 +4603,7 @@
           <t>主胜 | 主胜 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜 | 主胜 | 主胜/平局 | 主胜</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr"/>
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="8" t="inlineStr"/>
@@ -4704,7 +4617,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>从 14 场挑置信最高的 9 场单选;9 场全对即中任选9。联合命中率见 parlay(相关性修正后更诚实)。</t>
         </is>
@@ -4714,7 +4627,7 @@
       <c r="F16" s="9" t="inlineStr"/>
       <c r="G16" s="9" t="inlineStr"/>
       <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -5177,7 +5090,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN3" s="12" t="inlineStr">
+      <c r="AN3" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5357,7 +5270,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN4" s="12" t="inlineStr">
+      <c r="AN4" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5537,7 +5450,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN5" s="12" t="inlineStr">
+      <c r="AN5" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5717,7 +5630,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN6" s="12" t="inlineStr">
+      <c r="AN6" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -5897,7 +5810,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN7" s="14" t="inlineStr">
+      <c r="AN7" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -6077,7 +5990,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN8" s="12" t="inlineStr">
+      <c r="AN8" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6257,7 +6170,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN9" s="12" t="inlineStr">
+      <c r="AN9" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6437,7 +6350,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN10" s="12" t="inlineStr">
+      <c r="AN10" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6593,7 +6506,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN11" s="12" t="inlineStr">
+      <c r="AN11" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6773,7 +6686,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN12" s="12" t="inlineStr">
+      <c r="AN12" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6953,7 +6866,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN13" s="12" t="inlineStr">
+      <c r="AN13" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -6985,15 +6898,15 @@
       </c>
       <c r="AT13" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AU13" s="8" t="n">
-        <v>30.03</v>
+        <v>23.05</v>
       </c>
       <c r="AV13" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日006 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7046,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN14" s="14" t="inlineStr">
+      <c r="AN14" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -7169,7 +7082,7 @@
         </is>
       </c>
       <c r="AU14" s="9" t="n">
-        <v>34.52</v>
+        <v>35</v>
       </c>
       <c r="AV14" s="9" t="inlineStr">
         <is>
@@ -7313,7 +7226,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN15" s="14" t="inlineStr">
+      <c r="AN15" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -7493,7 +7406,7 @@
           <t>新浪胜负彩欧洲四大机构 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw0290689.shtml+新浪胜负彩澳盘 https://sports.sina.com.cn/l/2026-05-28/doc-inhzmayw8757470.shtml+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-31/doc-inhzuetq6338450.shtml</t>
         </is>
       </c>
-      <c r="AN16" s="12" t="inlineStr">
+      <c r="AN16" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -7675,45 +7588,45 @@
       </c>
       <c r="AN17" s="12" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="AO17" s="8" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="AP17" s="8" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="AQ17" s="8" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AR17" s="8" t="inlineStr">
         <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="AS17" s="8" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
-        <is>
-          <t>客胜-客胜</t>
-        </is>
-      </c>
       <c r="AT17" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="AU17" s="8" t="n">
-        <v>22.17</v>
+        <v>8.59</v>
       </c>
       <c r="AV17" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7766,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN18" s="14" t="inlineStr">
+      <c r="AN18" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -8033,7 +7946,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN19" s="12" t="inlineStr">
+      <c r="AN19" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -8213,47 +8126,47 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN20" s="14" t="inlineStr">
+      <c r="AN20" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="AO20" s="9" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="AO20" s="9" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="AP20" s="9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="AQ20" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="AR20" s="9" t="inlineStr">
         <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="AS20" s="9" t="inlineStr">
+        <is>
           <t>客胜-客胜</t>
         </is>
       </c>
-      <c r="AS20" s="9" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
       <c r="AT20" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="AU20" s="9" t="n">
-        <v>8.539999999999999</v>
+        <v>42.05</v>
       </c>
       <c r="AV20" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8306,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN21" s="14" t="inlineStr">
+      <c r="AN21" s="12" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
@@ -8405,12 +8318,12 @@
       </c>
       <c r="AP21" s="8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="AQ21" s="8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="AR21" s="8" t="inlineStr">
@@ -8429,7 +8342,7 @@
         </is>
       </c>
       <c r="AU21" s="8" t="n">
-        <v>34.52</v>
+        <v>35</v>
       </c>
       <c r="AV21" s="8" t="inlineStr">
         <is>
@@ -8573,7 +8486,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN22" s="12" t="inlineStr">
+      <c r="AN22" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -8585,12 +8498,12 @@
       </c>
       <c r="AP22" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="AQ22" s="9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="AR22" s="9" t="inlineStr">
@@ -8609,7 +8522,7 @@
         </is>
       </c>
       <c r="AU22" s="9" t="n">
-        <v>31.15</v>
+        <v>23.05</v>
       </c>
       <c r="AV22" s="9" t="inlineStr">
         <is>
@@ -8753,7 +8666,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN23" s="12" t="inlineStr">
+      <c r="AN23" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -8933,7 +8846,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN24" s="12" t="inlineStr">
+      <c r="AN24" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -9113,7 +9026,7 @@
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN25" s="12" t="inlineStr">
+      <c r="AN25" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
@@ -9508,7 +9421,7 @@
           <t>常规｜赔率变化平稳；亚盘变化+0.5</t>
         </is>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.5）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -9708,7 +9621,7 @@
           <t>常规｜赔率变化平稳；亚盘变化+0.5</t>
         </is>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.5）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -9908,7 +9821,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
@@ -10108,7 +10021,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T10" s="13" t="inlineStr">
+      <c r="T10" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
@@ -10308,7 +10221,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T12" s="13" t="inlineStr">
+      <c r="T12" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
@@ -10371,11 +10284,11 @@
         </is>
       </c>
       <c r="L13" s="8" t="n">
-        <v>30.03</v>
+        <v>23.05</v>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
@@ -10471,7 +10384,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>34.52</v>
+        <v>35</v>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
@@ -10508,7 +10421,7 @@
           <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
-      <c r="T14" s="13" t="inlineStr">
+      <c r="T14" s="14" t="inlineStr">
         <is>
           <t>主判断：客胜，防主胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.54）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -10708,7 +10621,7 @@
           <t>常规｜赔率变化平稳；亚盘变化-0.25</t>
         </is>
       </c>
-      <c r="T16" s="13" t="inlineStr">
+      <c r="T16" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.86）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -10752,26 +10665,26 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
-        <v>22.17</v>
+        <v>8.59</v>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
@@ -10780,7 +10693,7 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>中高｜备选赔付不高，市场不排除</t>
+          <t>中高｜概率差过小</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr">
@@ -10810,7 +10723,7 @@
       </c>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.42）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：客胜，防主胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.42）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10821,7 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T18" s="13" t="inlineStr">
+      <c r="T18" s="14" t="inlineStr">
         <is>
           <t>主判断：客胜，防主胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.42）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -11052,26 +10965,26 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>8.539999999999999</v>
+        <v>42.05</v>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
@@ -11080,7 +10993,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>中高｜概率差过小</t>
+          <t>中高｜备选赔付不高，市场不排除</t>
         </is>
       </c>
       <c r="O20" s="9" t="inlineStr">
@@ -11108,9 +11021,9 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T20" s="13" t="inlineStr">
-        <is>
-          <t>主判断：客胜，防主胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.55）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+      <c r="T20" s="14" t="inlineStr">
+        <is>
+          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.55）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11075,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -11171,7 +11084,7 @@
         </is>
       </c>
       <c r="L21" s="8" t="n">
-        <v>34.52</v>
+        <v>35</v>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
@@ -11262,7 +11175,7 @@
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -11271,7 +11184,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>31.15</v>
+        <v>23.05</v>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
@@ -11308,7 +11221,7 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T22" s="13" t="inlineStr">
+      <c r="T22" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.65）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -11508,7 +11421,7 @@
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T24" s="13" t="inlineStr">
+      <c r="T24" s="14" t="inlineStr">
         <is>
           <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
@@ -13264,7 +13177,7 @@
       </c>
       <c r="AG13" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日006 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13693,7 @@
       </c>
       <c r="AG17" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14030,12 @@
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>均衡对抗/容错偏低</t>
+          <t>均衡偏主动</t>
         </is>
       </c>
       <c r="X20" s="9" t="inlineStr">
         <is>
-          <t>均衡对抗/容错偏低</t>
+          <t>均衡偏主动</t>
         </is>
       </c>
       <c r="Y20" s="9" t="inlineStr">
@@ -14167,7 +14080,7 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -15151,10 +15064,10 @@
         <v>0</v>
       </c>
       <c r="AA3" s="8" t="n">
-        <v>0.6401</v>
+        <v>0.6403</v>
       </c>
       <c r="AB3" s="8" t="n">
-        <v>0.1772</v>
+        <v>0.177</v>
       </c>
       <c r="AC3" s="8" t="n">
         <v>0.1827</v>
@@ -15198,7 +15111,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>德国 对 芬兰</t>
         </is>
@@ -15290,10 +15203,10 @@
         <v>0</v>
       </c>
       <c r="AA4" s="9" t="n">
-        <v>0.6665</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="AB4" s="9" t="n">
-        <v>0.1576</v>
+        <v>0.1573</v>
       </c>
       <c r="AC4" s="9" t="n">
         <v>0.1759</v>
@@ -15429,13 +15342,13 @@
         <v>0</v>
       </c>
       <c r="AA5" s="8" t="n">
-        <v>0.3875</v>
+        <v>0.3877</v>
       </c>
       <c r="AB5" s="8" t="n">
-        <v>0.2582</v>
+        <v>0.2579</v>
       </c>
       <c r="AC5" s="8" t="n">
-        <v>0.3543</v>
+        <v>0.3544</v>
       </c>
       <c r="AD5" s="8" t="n">
         <v>5</v>
@@ -15476,7 +15389,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>巴西 对 巴拿马</t>
         </is>
@@ -15568,13 +15481,13 @@
         <v>0</v>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>0.6674</v>
+        <v>0.6676</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>0.1588</v>
+        <v>0.1585</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>0.1738</v>
+        <v>0.1739</v>
       </c>
       <c r="AD6" s="9" t="n">
         <v>5</v>
@@ -15707,13 +15620,13 @@
         <v>0.33</v>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>0.3599</v>
+        <v>0.3602</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>0.2585</v>
+        <v>0.2583</v>
       </c>
       <c r="AC7" s="8" t="n">
-        <v>0.3816</v>
+        <v>0.3815</v>
       </c>
       <c r="AD7" s="8" t="n">
         <v>5</v>
@@ -15754,7 +15667,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>挪威 对 瑞典</t>
         </is>
@@ -15846,13 +15759,13 @@
         <v>0</v>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>0.4604</v>
+        <v>0.4606</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>0.2474</v>
+        <v>0.2471</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>0.2922</v>
+        <v>0.2923</v>
       </c>
       <c r="AD8" s="9" t="n">
         <v>5</v>
@@ -15985,10 +15898,10 @@
         <v>0</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6208</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>0.1892</v>
+        <v>0.1889</v>
       </c>
       <c r="AC9" s="8" t="n">
         <v>0.1903</v>
@@ -16032,7 +15945,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>奥地利 对 突尼斯</t>
         </is>
@@ -16124,10 +16037,10 @@
         <v>0</v>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>0.5272</v>
+        <v>0.5275</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>0.2317</v>
+        <v>0.2314</v>
       </c>
       <c r="AC10" s="9" t="n">
         <v>0.2411</v>
@@ -16263,13 +16176,13 @@
         <v>0</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>0.5314</v>
+        <v>0.5317</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>0.2064</v>
+        <v>0.206</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>0.2622</v>
+        <v>0.2623</v>
       </c>
       <c r="AD11" s="8" t="n">
         <v>4</v>
@@ -16310,7 +16223,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>加拿大 对 乌兹别克斯坦</t>
         </is>
@@ -16402,10 +16315,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>0.5357</v>
+        <v>0.536</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>0.2295</v>
+        <v>0.2292</v>
       </c>
       <c r="AC12" s="9" t="n">
         <v>0.2348</v>
@@ -16488,41 +16401,41 @@
         <v>0.4144</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.2822</v>
+        <v>0.2708</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.3034</v>
+        <v>0.3148</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>0.4049</v>
+        <v>0.3824</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>0.2868</v>
+        <v>0.2802</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>0.3083</v>
+        <v>0.3374</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>0.431</v>
+        <v>0.4269</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>0.2639</v>
+        <v>0.2643</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>0.3052</v>
+        <v>0.3089</v>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>1-1:12.5% / 1-0:10.5% / 0-1:9.1%</t>
+          <t>1-1:12.7% / 1-0:10.6% / 0-1:9.2%</t>
         </is>
       </c>
       <c r="U13" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V13" s="8" t="n">
-        <v>30.03</v>
+        <v>23.05</v>
       </c>
       <c r="W13" s="8" t="inlineStr">
         <is>
@@ -16535,26 +16448,26 @@
         </is>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>-0.0386</v>
+        <v>-0.0404</v>
       </c>
       <c r="Z13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>0.4152</v>
+        <v>0.3708</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>0.2567</v>
+        <v>0.2502</v>
       </c>
       <c r="AC13" s="8" t="n">
-        <v>0.3281</v>
+        <v>0.379</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>5</v>
       </c>
       <c r="AE13" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日006 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AF13" s="8" t="n">
@@ -16588,7 +16501,7 @@
           <t>瑞超</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>赫根 对 哈马比</t>
         </is>
@@ -16624,35 +16537,35 @@
         </is>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.2925</v>
+        <v>0.2871</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.2347</v>
+        <v>0.2401</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>0.4728</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>0.3225</v>
+        <v>0.3136</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0.2667</v>
+        <v>0.254</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0.4108</v>
+        <v>0.4324</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>0.2921</v>
+        <v>0.2798</v>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0.2626</v>
+        <v>0.2649</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0.4454</v>
+        <v>0.4554</v>
       </c>
       <c r="T14" s="9" t="inlineStr">
         <is>
-          <t>1-1:12.7% / 0-1:11.4% / 1-0:8.8%</t>
+          <t>1-1:12.7% / 0-1:11.4% / 1-2:9.1%</t>
         </is>
       </c>
       <c r="U14" s="9" t="inlineStr">
@@ -16661,7 +16574,7 @@
         </is>
       </c>
       <c r="V14" s="9" t="n">
-        <v>34.52</v>
+        <v>35</v>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -16674,19 +16587,19 @@
         </is>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>-0.0593</v>
+        <v>0.0108</v>
       </c>
       <c r="Z14" s="9" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>0.3612</v>
+        <v>0.3227</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>0.2487</v>
+        <v>0.2298</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>0.3901</v>
+        <v>0.4475</v>
       </c>
       <c r="AD14" s="9" t="n">
         <v>5</v>
@@ -16819,13 +16732,13 @@
         <v>0</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>0.3872</v>
+        <v>0.3817</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>0.255</v>
+        <v>0.2515</v>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>0.3578</v>
+        <v>0.3668</v>
       </c>
       <c r="AD15" s="8" t="n">
         <v>5</v>
@@ -16866,7 +16779,7 @@
           <t>芬超</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>AC 奥卢 对 雅罗</t>
         </is>
@@ -16958,10 +16871,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="n">
-        <v>0.5189</v>
+        <v>0.5192</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>0.2322</v>
+        <v>0.2319</v>
       </c>
       <c r="AC16" s="9" t="n">
         <v>0.2489</v>
@@ -17012,64 +16925,64 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>客胜-客胜</t>
-        </is>
-      </c>
       <c r="K17" s="8" t="n">
-        <v>0.4136</v>
+        <v>0.3461</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.2633</v>
+        <v>0.3006</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3231</v>
+        <v>0.3533</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>0.3771</v>
+        <v>0.339</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>0.2797</v>
+        <v>0.2945</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>0.3432</v>
+        <v>0.3665</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>0.367</v>
+        <v>0.3393</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>0.2798</v>
+        <v>0.2806</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>0.3533</v>
+        <v>0.3802</v>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>1-1:13.2% / 1-0:10.7% / 0-1:10.5%</t>
+          <t>1-1:13.2% / 0-1:10.9% / 1-0:10.2%</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
@@ -17078,7 +16991,7 @@
         </is>
       </c>
       <c r="V17" s="8" t="n">
-        <v>22.17</v>
+        <v>8.59</v>
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
@@ -17091,33 +17004,33 @@
         </is>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>0.1374</v>
+        <v>-0.1697</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>0.3737</v>
+        <v>0.3389</v>
       </c>
       <c r="AB17" s="8" t="n">
-        <v>0.2502</v>
+        <v>0.2563</v>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>0.3761</v>
+        <v>0.4048</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>5</v>
       </c>
       <c r="AE17" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：日职，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AG17" s="8" t="n">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="AH17" s="8" t="inlineStr">
         <is>
@@ -17144,7 +17057,7 @@
           <t>日职</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>清水鼓动 对 横滨水手</t>
         </is>
@@ -17236,13 +17149,13 @@
         <v>0</v>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>0.3891</v>
+        <v>0.4105</v>
       </c>
       <c r="AB18" s="9" t="n">
-        <v>0.2361</v>
+        <v>0.2306</v>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>0.3748</v>
+        <v>0.3589</v>
       </c>
       <c r="AD18" s="9" t="n">
         <v>4</v>
@@ -17375,13 +17288,13 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="n">
-        <v>0.5575</v>
+        <v>0.5578</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>0.191</v>
+        <v>0.1906</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>0.2515</v>
+        <v>0.2516</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>4</v>
@@ -17422,71 +17335,71 @@
           <t>瑞超</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>韦斯特罗斯 对 哥德堡</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
           <t>客胜-客胜</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
       <c r="K20" s="9" t="n">
-        <v>0.3533</v>
+        <v>0.5</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.2897</v>
+        <v>0.2422</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>0.357</v>
+        <v>0.2578</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>0.3688</v>
+        <v>0.472</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>0.2828</v>
+        <v>0.2558</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0.3485</v>
+        <v>0.2722</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>0.3962</v>
+        <v>0.474</v>
       </c>
       <c r="R20" s="9" t="n">
-        <v>0.2678</v>
+        <v>0.2619</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0.3361</v>
+        <v>0.2642</v>
       </c>
       <c r="T20" s="9" t="inlineStr">
         <is>
-          <t>1-1:12.5% / 1-0:10.1% / 0-1:9.3%</t>
+          <t>1-1:12.2% / 1-0:11.6% / 2-1:9.1%</t>
         </is>
       </c>
       <c r="U20" s="9" t="inlineStr">
@@ -17495,11 +17408,11 @@
         </is>
       </c>
       <c r="V20" s="9" t="n">
-        <v>8.539999999999999</v>
+        <v>42.05</v>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>⚪ 慎选/观望</t>
+          <t>🟡 可选</t>
         </is>
       </c>
       <c r="X20" s="9" t="inlineStr">
@@ -17508,33 +17421,33 @@
         </is>
       </c>
       <c r="Y20" s="9" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Z20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA20" s="9" t="n">
-        <v>0.4033</v>
+        <v>0.5652</v>
       </c>
       <c r="AB20" s="9" t="n">
-        <v>0.2415</v>
+        <v>0.2003</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>0.3552</v>
+        <v>0.2345</v>
       </c>
       <c r="AD20" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，客胜概率领先主胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AF20" s="9" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" s="9" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AH20" s="9" t="inlineStr">
         <is>
@@ -17578,12 +17491,12 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -17597,35 +17510,35 @@
         </is>
       </c>
       <c r="K21" s="8" t="n">
-        <v>0.2925</v>
+        <v>0.2871</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.2347</v>
+        <v>0.2401</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>0.4728</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>0.3112</v>
+        <v>0.2979</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>0.2498</v>
+        <v>0.2492</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>0.439</v>
+        <v>0.4529</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>0.2116</v>
+        <v>0.2105</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>0.2491</v>
+        <v>0.2493</v>
       </c>
       <c r="S21" s="8" t="n">
-        <v>0.5394</v>
+        <v>0.5403</v>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>0-1:12.8% / 1-1:11.8% / 0-2:10.4%</t>
+          <t>0-1:12.8% / 1-1:11.9% / 0-2:10.4%</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -17634,7 +17547,7 @@
         </is>
       </c>
       <c r="V21" s="8" t="n">
-        <v>34.52</v>
+        <v>35</v>
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
@@ -17653,16 +17566,16 @@
         <v>0</v>
       </c>
       <c r="AA21" s="8" t="n">
-        <v>0.3816</v>
+        <v>0.3166</v>
       </c>
       <c r="AB21" s="8" t="n">
-        <v>0.2291</v>
+        <v>0.228</v>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>0.3893</v>
+        <v>0.4554</v>
       </c>
       <c r="AD21" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE21" s="8" t="inlineStr">
         <is>
@@ -17700,7 +17613,7 @@
           <t>瑞超</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>代格福什 对 布鲁马波</t>
         </is>
@@ -17717,12 +17630,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -17736,35 +17649,35 @@
         </is>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.4453</v>
+        <v>0.4144</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.2743</v>
+        <v>0.2708</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>0.2804</v>
+        <v>0.3148</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>0.4317</v>
+        <v>0.404</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>0.281</v>
+        <v>0.2756</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0.2873</v>
+        <v>0.3204</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0.4797</v>
+        <v>0.4616</v>
       </c>
       <c r="R22" s="9" t="n">
-        <v>0.2583</v>
+        <v>0.2578</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>0.2621</v>
+        <v>0.2806</v>
       </c>
       <c r="T22" s="9" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:11.5% / 2-1:9%</t>
+          <t>1-1:12.2% / 1-0:11.3% / 2-1:8.9%</t>
         </is>
       </c>
       <c r="U22" s="9" t="inlineStr">
@@ -17773,7 +17686,7 @@
         </is>
       </c>
       <c r="V22" s="9" t="n">
-        <v>31.15</v>
+        <v>23.05</v>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -17786,22 +17699,22 @@
         </is>
       </c>
       <c r="Y22" s="9" t="n">
-        <v>-0.0871</v>
+        <v>-0.1505</v>
       </c>
       <c r="Z22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AA22" s="9" t="n">
-        <v>0.427</v>
+        <v>0.3752</v>
       </c>
       <c r="AB22" s="9" t="n">
-        <v>0.2409</v>
+        <v>0.2466</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>0.3321</v>
+        <v>0.3782</v>
       </c>
       <c r="AD22" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE22" s="9" t="inlineStr">
         <is>
@@ -17931,10 +17844,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="n">
-        <v>0.481</v>
+        <v>0.4814</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>0.2227</v>
+        <v>0.2223</v>
       </c>
       <c r="AC23" s="8" t="n">
         <v>0.2963</v>
@@ -17978,7 +17891,7 @@
           <t>国际赛</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>捷克 对 科索沃</t>
         </is>
@@ -18070,13 +17983,13 @@
         <v>0</v>
       </c>
       <c r="AA24" s="9" t="n">
-        <v>0.4856</v>
+        <v>0.4859</v>
       </c>
       <c r="AB24" s="9" t="n">
-        <v>0.2265</v>
+        <v>0.226</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>0.2879</v>
+        <v>0.2881</v>
       </c>
       <c r="AD24" s="9" t="n">
         <v>4</v>
@@ -18209,10 +18122,10 @@
         <v>0</v>
       </c>
       <c r="AA25" s="8" t="n">
-        <v>0.4016</v>
+        <v>0.402</v>
       </c>
       <c r="AB25" s="8" t="n">
-        <v>0.2462</v>
+        <v>0.2458</v>
       </c>
       <c r="AC25" s="8" t="n">
         <v>0.3522</v>

--- a/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
+++ b/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
@@ -4144,7 +4144,7 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>土耳其 对 北马其顿</t>
+          <t>巴西 对 巴拿马</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
@@ -4154,27 +4154,27 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>胆</t>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>双选</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
+          <t>主 76.5% / 平 18.5% / 客 5%</t>
         </is>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>🟢 较高 (97.6)</t>
+          <t>🟢 较高 (95.8)</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢一档(市场热门84%·回测命中~88%)；双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>瑞士 对 约旦</t>
+          <t>德国 对 芬兰</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>胆</t>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>双选</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>主 76.4% / 平 18.2% / 客 5.4%</t>
+          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (97.6)</t>
+          <t>🟢 较高 (95.9)</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢一档(市场热门83%·回测命中~88%)；双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>德国 对 芬兰</t>
+          <t>瑞士 对 约旦</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -4244,27 +4244,27 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>双选</t>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>胆</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
+          <t>主 76.4% / 平 18.2% / 客 5.4%</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>🟢 较高 (95.9)</t>
+          <t>🟢 较高 (97.6)</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢一档(市场热门77%·回测命中~80%)；✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>巴西 对 巴拿马</t>
+          <t>土耳其 对 北马其顿</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
@@ -4289,27 +4289,27 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>双选</t>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>胆</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>主 76.5% / 平 18.5% / 客 5%</t>
+          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (95.8)</t>
+          <t>🟢 较高 (97.6)</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢一档(市场热门75%·回测命中~80%)；✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>双选(差 49%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢二档(市场热门71%·回测命中~73%)；双选(差 49%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>奥地利 对 突尼斯</t>
+          <t>加拿大 对 乌兹别克斯坦</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -4379,27 +4379,27 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>胆</t>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>双选</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>主 57.9% / 平 25.5% / 客 16.5%</t>
+          <t>主 57.9% / 平 26.4% / 客 15.7%</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (61.1)</t>
+          <t>🟢 较高 (60.3)</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟡三档(市场热门64%·回测命中~63%)；⚠ 平局 ≥22% 强制覆盖；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>加拿大 对 乌兹别克斯坦</t>
+          <t>奥地利 对 突尼斯</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -4424,27 +4424,27 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>胆</t>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>双选</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>主 57.9% / 平 26.4% / 客 15.7%</t>
+          <t>主 57.9% / 平 25.5% / 客 16.5%</t>
         </is>
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>🟢 较高 (60.3)</t>
+          <t>🟢 较高 (61.1)</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟡三档(市场热门60%·回测命中~63%)；⚠ 平局 ≥22% 强制覆盖；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>⚠ 平局 ≥22% 强制覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日008 胜平负方向强制一致</t>
+          <t>🟡三档(市场热门57%·回测命中~63%)；⚠ 平局 ≥22% 强制覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日008 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>胆</t>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>双选</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟠偏弱(市场热门50%·回测命中~50%)；⚠ 平局 ≥22% 强制覆盖；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>主胜 | 主胜 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜 | 主胜 | 主胜/平局 | 主胜</t>
+          <t>主胜/平局 | 主胜/平局 | 主胜 | 主胜 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜/平局</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr"/>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="AH3" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI3" s="8" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="AH4" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI4" s="9" t="inlineStr"/>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="AH5" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI5" s="8" t="inlineStr"/>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="AH6" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI6" s="9" t="inlineStr"/>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="AH7" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="AI7" s="8" t="inlineStr"/>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="AH8" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="AI8" s="9" t="inlineStr"/>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="AH9" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="AI9" s="8" t="inlineStr"/>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AH10" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="AI10" s="9" t="inlineStr"/>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AH11" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="AI11" s="8" t="inlineStr"/>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AH12" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:01.000Z</t>
         </is>
       </c>
       <c r="AI12" s="9" t="inlineStr"/>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="AH13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI13" s="8" t="inlineStr"/>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="AH14" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI14" s="9" t="inlineStr"/>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="AH15" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI15" s="8" t="inlineStr"/>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AH16" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31T01:57:58.000Z</t>
+          <t>2026-05-31T06:00:02.000Z</t>
         </is>
       </c>
       <c r="AI16" s="9" t="inlineStr"/>

--- a/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
+++ b/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据缺失·未预测" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全面审计'!$A$2:$C$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全面审计'!$A$2:$C$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'出表自检'!$A$2:$I$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'神选·竞彩'!$A$2:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'神选·14场'!$A$2:$J$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'神选·任选9'!$A$2:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'神选·任选9'!$A$2:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'赔率变化'!$A$2:$AV$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'融合判断'!$A$2:$T$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'大小球·阵容'!$A$2:$AG$27</definedName>
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -667,12 +667,12 @@
       <c r="A4" s="9" t="inlineStr"/>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>✓ 模块结构</t>
+          <t>⚠ 模块结构</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>通过 48/49,错误 0,警告 1</t>
+          <t>通过 47/49,错误 1,警告 1</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>P0 1 / P1 6 / P2 1</t>
+          <t>P0 2 / P1 6 / P2 1</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>缺陷 [P0] 可用赔率不完整：23/26；缺口=瑞士 对 约旦、德国 对 芬兰、巴西 对 巴拿马(数据时效/就绪类,出表新鲜度由 source-gate 硬拦)</t>
+          <t>模块结构 1 项告警(多为缺运行时文件/数据,新鲜度由 source-gate 硬拦)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>缺陷 [P1] 完整赔率不完整：13/26；缺口=哥伦比亚 对 哥斯达黎加、冈山绿雉 对 浦和红钻、清水鼓动 对 横滨水手、日本 对 冰岛、韦斯特罗斯 对 哥德堡、赫根 对 哈马比 等13场</t>
+          <t>缺陷 [P0] 可用赔率不完整：23/26；缺口=瑞士 对 约旦、德国 对 芬兰、巴西 对 巴拿马(数据时效/就绪类,出表新鲜度由 source-gate 硬拦)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>缺陷 [P1] 缺少Elo/球队强度</t>
+          <t>缺陷 [P1] 完整赔率不完整：13/26；缺口=哥伦比亚 对 哥斯达黎加、冈山绿雉 对 浦和红钻、清水鼓动 对 横滨水手、日本 对 冰岛、韦斯特罗斯 对 哥德堡、赫根 对 哈马比 等13场</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>缺陷 [P1] 缺少近期状态/赛程强度</t>
+          <t>缺陷 [P0] 闸门失败：14场官方源失败：期号：缺失，场次：0(数据时效/就绪类,出表新鲜度由 source-gate 硬拦)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>缺陷 [P1] 缺少伤停与阵容</t>
+          <t>缺陷 [P1] 缺少Elo/球队强度</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>缺陷 [P1] 缺少预计首发</t>
+          <t>缺陷 [P1] 缺少近期状态/赛程强度</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>缺陷 [P1] 缺少xG/射门质量</t>
+          <t>缺陷 [P1] 缺少伤停与阵容</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>缺陷 [P2] 可选层未完全覆盖：天气/场地/旅行、新闻舆情/战意</t>
+          <t>缺陷 [P1] 缺少预计首发</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>能力:2 个 P0 层未完全就绪(多为今日实时数据未刷新)</t>
+          <t>缺陷 [P1] 缺少xG/射门质量</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>逐场自检:[哥伦比亚 vs 哥斯达黎加] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>缺陷 [P2] 可选层未完全覆盖：天气/场地/旅行、新闻舆情/战意</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>逐场自检:[清水鼓动 vs 横滨水手] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>能力:2 个 P0 层未完全就绪(多为今日实时数据未刷新)</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>逐场自检:[日本 vs 冰岛] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>逐场自检:[哥伦比亚 vs 哥斯达黎加] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>逐场自检:[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>逐场自检:[清水鼓动 vs 横滨水手] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>逐场自检:[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>逐场自检:[日本 vs 冰岛] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
@@ -958,22 +958,48 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
+          <t>逐场自检:[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>逐场自检:[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="9" t="inlineStr"/>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
           <t>逐场自检:[美国 vs 塞内加尔] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C28"/>
+  <autoFilter ref="A2:C30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A30:C30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4065,7 +4091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4611,17 +4637,9 @@
       <c r="I15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
+      <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>从 14 场挑置信最高的 9 场单选;9 场全对即中任选9。联合命中率见 parlay(相关性修正后更诚实)。</t>
-        </is>
-      </c>
+      <c r="C16" s="14" t="inlineStr"/>
       <c r="D16" s="17" t="inlineStr"/>
       <c r="E16" s="9" t="inlineStr"/>
       <c r="F16" s="9" t="inlineStr"/>
@@ -4629,18 +4647,75 @@
       <c r="H16" s="9" t="inlineStr"/>
       <c r="I16" s="14" t="inlineStr"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>⭐ 最优票(54注·预算64)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>整票全中 20%(全单选仅 2.4%)</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>最优覆盖</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>巴西 | 德国 | 瑞士 | 土耳其 | 哥伦比亚 | 加拿大(主胜/平局) | 奥地利(主胜/平局/客胜) | AC 奥卢(主胜/平局/客胜) | 挪威(主胜/平局/客胜)</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>从 14 场挑置信最高的 9 场单选;9 场全对即中任选9。联合命中率见 parlay(相关性修正后更诚实)。</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I18"/>
+  <autoFilter ref="A2:I21"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
+++ b/推荐产出/神选-竞彩推荐_2026-05-31.xlsx
@@ -16,17 +16,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据缺失·未预测" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全面审计'!$A$2:$C$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'出表自检'!$A$2:$I$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'神选·竞彩'!$A$2:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全面审计'!$A$2:$C$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'出表自检'!$A$2:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'神选·竞彩'!$A$2:$M$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'神选·14场'!$A$2:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'神选·任选9'!$A$2:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'赔率变化'!$A$2:$AV$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'融合判断'!$A$2:$T$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'大小球·阵容'!$A$2:$AG$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'复盘对比'!$A$2:$AK$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'赔率变化'!$A$2:$AV$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'融合判断'!$A$2:$T$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'大小球·阵容'!$A$2:$AG$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'复盘对比'!$A$2:$AK$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'模型健康'!$A$2:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'数据缺失·未预测'!$A$2:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'数据缺失·未预测'!$A$2:$D$5</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -132,12 +132,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFB300"/>
+        <fgColor rgb="FFE1F5FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1F5FE"/>
+        <fgColor rgb="FFFFB300"/>
       </patternFill>
     </fill>
   </fills>
@@ -248,10 +248,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>blocker 0 / warning 6</t>
+          <t>blocker 0 / warning 9</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>进推荐 23 场,造假 0,数据缺失已诚实单列 3 场,方向不一致 0</t>
+          <t>进推荐 26 场,造假 0,数据缺失已诚实单列 0 场,方向不一致 0</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>胜负平 ✓23 · 让球 ✓23 · 比分 ✓23 · 半全场 ✓23</t>
+          <t>胜负平 ✓26 · 让球 ✓26 · 比分 ✓26 · 半全场 ✓26</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>逐场自检:[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>逐场自检:[瑞士 vs 约旦] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>逐场自检:[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>逐场自检:[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
@@ -984,22 +984,61 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
+          <t>逐场自检:[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>逐场自检:[德国 vs 芬兰] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="9" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
           <t>逐场自检:[美国 vs 塞内加尔] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>逐场自检:[巴西 vs 巴拿马] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C30"/>
+  <autoFilter ref="A2:C33"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1073,7 +1112,7 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>23 场已审核</t>
+          <t>26 场已审核</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1175,81 +1214,33 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>周日007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>瑞士 vs 约旦</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>未捕获实时赔率且该队不在 Dixon-Coles 训练集——无真实先验,按规则不预测(不编造)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>周日010</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>德国 vs 芬兰</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>未捕获实时赔率且该队不在 Dixon-Coles 训练集——无真实先验,按规则不预测(不编造)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>周日012</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>巴西 vs 巴拿马</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>未捕获实时赔率且该队不在 Dixon-Coles 训练集——无真实先验,按规则不预测(不编造)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+          <t>本期所有场次均有真实先验(赔率/DC),无剔除场。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D7"/>
+  <autoFilter ref="A2:D5"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1261,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1290,17 +1281,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>场次 23 · 竞彩 9 · 14场 14 · 任选9 9</t>
+          <t>场次 26 · 竞彩 12 · 14场 14 · 任选9 9</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>DC真跑 17 · 仅赔率 6 · 融合fire 0</t>
+          <t>DC真跑 17 · 仅赔率 9 · 融合fire 0</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>拦截 0 · 提示 6</t>
+          <t>拦截 0 · 提示 9</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -2299,12 +2290,12 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>周日008</t>
+          <t>周日007</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>AC奥卢 vs 雅罗</t>
+          <t>瑞士 vs 约旦</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2346,12 +2337,12 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日008</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>捷克 vs 科索沃</t>
+          <t>AC奥卢 vs 雅罗</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2393,12 +2384,12 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>周日011</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>美国 vs 塞内加尔</t>
+          <t>捷克 vs 科索沃</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -2440,52 +2431,148 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>⚠ 提示</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="8" t="inlineStr"/>
-      <c r="D27" s="8" t="inlineStr"/>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="8" t="inlineStr"/>
+          <t>周日010</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>德国 vs 芬兰</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>⚠仅赔率</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>[哥伦比亚 vs 哥斯达黎加] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr"/>
-      <c r="C28" s="9" t="inlineStr"/>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="9" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
-      <c r="I28" s="9" t="inlineStr"/>
+          <t>周日011</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>美国 vs 塞内加尔</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>⚠仅赔率</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>[清水鼓动 vs 横滨水手] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr"/>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>巴西 vs 巴拿马</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>⚠仅赔率</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>[日本 vs 冰岛] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>⚠ 提示</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr"/>
@@ -2500,7 +2587,7 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>[哥伦比亚 vs 哥斯达黎加] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr"/>
@@ -2515,7 +2602,7 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>[清水鼓动 vs 横滨水手] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr"/>
@@ -2530,7 +2617,7 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>[美国 vs 塞内加尔] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+          <t>[日本 vs 冰岛] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr"/>
@@ -2542,18 +2629,108 @@
       <c r="H33" s="8" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr"/>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>[瑞士 vs 约旦] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="9" t="inlineStr"/>
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>[AC奥卢 vs 雅罗] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>[捷克 vs 科索沃] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="9" t="inlineStr"/>
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>[德国 vs 芬兰] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>[美国 vs 塞内加尔] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr"/>
+      <c r="C38" s="9" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>[巴西 vs 巴拿马] DC 未覆盖(纯赔率换算,模型核心未参与)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="8" t="inlineStr"/>
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I35"/>
+  <autoFilter ref="A2:I41"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A41:I41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2565,7 +2742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3072,216 +3249,417 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>周日007</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>🌍 国家队赛</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>瑞士 vs 约旦</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>05-31 21:00</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>让 -2 → 主胜 覆盖16.4%</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>1-0 (13%) | 备 2-0 (13%), 2-1 (9%)</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>主胜-主胜 (37%) | 另 平局-主胜 (20%)</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>主 67% / 平 25.7% / 客 7.3%</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>公认 favorite</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>🟢 较高 (59.8) · 🟢 建议下注</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；融合信号: season-phase(late)、competition-type(国际赛)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
           <t>周日008</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>⚽ 联赛</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>AC奥卢 vs 雅罗</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>05-31 21:00</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>让 -1 → 主胜 覆盖45.5%</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>2-0 (13%) | 备 1-0 (12%), 2-1 (9%)</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>主胜-主胜 (45%) | 另 平局-主胜 (21%)</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>主 57.9% / 平 23% / 客 19%</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>标准</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>📊 历史同情境大球(&gt;2.5)52%、均2.72球(1402场),大小球均衡
 🔀 历史同情境(开→收盘口平稳):主队(热门)兑现 54%(887场)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>🟢 较高 (57.4) · 🟡 可选 · EV -10.8%</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t>经模型综合分析：芬兰超级联赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>周日009</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>🌍 国家队赛</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>捷克 vs 科索沃</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>05-31 22:00</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>让 -1 → 主胜 覆盖30.3%</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>1-0 (12%) | 备 2-0 (11%), 2-1 (10%)</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>主胜-主胜 (33%) | 另 平局-主胜 (19%)</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>主 57.4% / 平 25.5% / 客 17.2%</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>🟢 较高 (54.2) · 🟡 可选 · EV -13.4%</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="inlineStr">
-        <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>周日009</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>🌍 国家队赛</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>捷克 vs 科索沃</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>05-31 22:00</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>让 -1 → 主胜 覆盖30.3%</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>1-0 (12%) | 备 2-0 (11%), 2-1 (10%)</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>主胜-主胜 (33%) | 另 平局-主胜 (19%)</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>主 57.4% / 平 25.5% / 客 17.2%</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>🟢 较高 (54.2) · 🟡 可选 · EV -13.4%</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>周日010</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>🌍 国家队赛</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>德国 vs 芬兰</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>06-01 02:45</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>让 -2 → 主胜 覆盖16.4%</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>1-0 (13%) | 备 2-0 (13%), 2-1 (9%)</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜 (37%) | 另 平局-主胜 (20%)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>主 66.9% / 平 25.6% / 客 7.5%</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>公认 favorite</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>🟢 较高 (59.8) · 🟢 建议下注</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；融合信号: season-phase(late)、competition-type(国际赛)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>周日011</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>🌍 国家队赛</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>美国 vs 塞内加尔</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>06-01 03:30</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>让 -1 → 主胜 覆盖20.5%</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>1-0 (10%) | 备 2-1 (9%)</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>主胜-主胜 (24%) | 另 平局-主胜 (15%)</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>主 35.9% / 平 28.9% / 客 35.2%</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>⚠ 高(弱势 ≥25%)</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
         </is>
       </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>🔴 低 (9) · ⚪ 慎选/观望 · EV -12.7%</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>经模型综合分析：国际赛，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>🌍 国家队赛</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>巴西 vs 巴拿马</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>06-01 05:30</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>让 -2 → 主胜 覆盖16.7%</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>1-0 (14%) | 备 2-0 (13%), 2-1 (9%)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜 (38%) | 另 平局-主胜 (21%)</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>主 67.5% / 平 25.7% / 客 6.7%</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>公认 favorite</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>📊 历史同情境大球(&gt;2.5)51%、均2.72球(41379场),大小球均衡</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>🟢 较高 (60.7) · 🟢 建议下注</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；融合信号: season-phase(late)、competition-type(国际赛)、streak(主drawing×1 客losing×3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M13"/>
+  <autoFilter ref="A2:M16"/>
   <mergeCells count="2">
-    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A16:M16"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3389,17 +3767,17 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>胆</t>
+          <t>双选</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>主 76.4% / 平 18.2% / 客 5.4%</t>
+          <t>主 67% / 平 25.7% / 客 7.3%</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -3409,12 +3787,12 @@
       </c>
       <c r="I3" s="16" t="inlineStr">
         <is>
-          <t>🟢 较高 (97.6)</t>
+          <t>🟢 较高 (59.8)</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>✅ 胆码；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日007 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3442,14 +3820,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
+          <t>主 66.9% / 平 25.6% / 客 7.5%</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
@@ -3459,12 +3837,12 @@
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (95.9)</t>
+          <t>🟢 较高 (59.8)</t>
         </is>
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>双选(概率差 58%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日010 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3870,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3542,14 +3920,14 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>主 76.5% / 平 18.5% / 客 5%</t>
+          <t>主 67.5% / 平 25.7% / 客 6.7%</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -3559,12 +3937,12 @@
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (95.8)</t>
+          <t>🟢 较高 (60.7)</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>双选(概率差 58%)；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:公认 favorite；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日012 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3970,7 @@
           <t>客胜/平局</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3642,7 +4020,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3692,7 +4070,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -3742,7 +4120,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -3792,7 +4170,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3839,12 +4217,12 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>双选</t>
+          <t>胆</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -3864,7 +4242,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>⚠ 平局 ≥25% 强制覆盖,搏爆冷；爆冷:标准；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>✅ 胆码；爆冷:标准；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3892,7 +4270,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3942,7 +4320,7 @@
           <t>客胜/主胜</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -3992,7 +4370,7 @@
           <t>客胜/平局</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4042,7 +4420,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4183,24 +4561,24 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>主 76.5% / 平 18.5% / 客 5%</t>
+          <t>主 67.5% / 平 25.7% / 客 6.7%</t>
         </is>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>🟢 较高 (95.8)</t>
+          <t>🟢 较高 (60.7)</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>🟢一档(市场热门84%·回测命中~88%)；双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢一档(市场热门84%·回测命中~88%)；⚠ 平局 ≥22% 强制覆盖；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日012 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4228,24 +4606,24 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>主 76.4% / 平 18.1% / 客 5.5%</t>
+          <t>主 66.9% / 平 25.6% / 客 7.5%</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>🟢 较高 (95.9)</t>
+          <t>🟢 较高 (59.8)</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>🟢一档(市场热门83%·回测命中~88%)；双选(差 58%)；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢一档(市场热门83%·回测命中~88%)；⚠ 平局 ≥22% 强制覆盖；经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日010 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4270,27 +4648,27 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>胆</t>
+          <t>双选</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>主 76.4% / 平 18.2% / 客 5.4%</t>
+          <t>主 67% / 平 25.7% / 客 7.3%</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>🟢 较高 (97.6)</t>
+          <t>🟢 较高 (59.8)</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>🟢一档(市场热门77%·回测命中~80%)；✅ 胆(高置信)；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>🟢一档(市场热门77%·回测命中~80%)；⚠ 平局 ≥22% 强制覆盖；经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日007 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4696,7 @@
           <t>主胜</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>胆</t>
         </is>
@@ -4363,7 +4741,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4408,7 +4786,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4453,7 +4831,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4498,7 +4876,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4543,7 +4921,7 @@
           <t>主胜/平局</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>双选</t>
         </is>
@@ -4603,12 +4981,12 @@
       <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>独立估计 2.4%</t>
+          <t>独立估计 1.6%</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>相关性修正 5%</t>
+          <t>相关性修正 3.4%</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr"/>
@@ -4626,7 +5004,7 @@
       <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>主胜/平局 | 主胜/平局 | 主胜 | 主胜 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜/平局</t>
+          <t>主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜/平局 | 主胜/平局</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr"/>
@@ -4656,7 +5034,7 @@
       <c r="B17" s="8" t="inlineStr"/>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>整票全中 20%(全单选仅 2.4%)</t>
+          <t>整票全中 13.6%(全单选仅 1.6%)</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr"/>
@@ -4727,7 +5105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV27"/>
+  <dimension ref="A1:AV30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5182,7 +5560,7 @@
       </c>
       <c r="AQ3" s="8" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="AR3" s="8" t="inlineStr">
@@ -5197,15 +5575,15 @@
       </c>
       <c r="AT3" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AU3" s="8" t="n">
-        <v>97.58</v>
+        <v>59.77</v>
       </c>
       <c r="AV3" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日007 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5740,7 @@
       </c>
       <c r="AQ4" s="9" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="AR4" s="9" t="inlineStr">
@@ -5381,11 +5759,11 @@
         </is>
       </c>
       <c r="AU4" s="9" t="n">
-        <v>95.84999999999999</v>
+        <v>59.79</v>
       </c>
       <c r="AV4" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日010 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -5722,7 +6100,7 @@
       </c>
       <c r="AQ6" s="9" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="AR6" s="9" t="inlineStr">
@@ -5741,11 +6119,11 @@
         </is>
       </c>
       <c r="AU6" s="9" t="n">
-        <v>95.76000000000001</v>
+        <v>60.71</v>
       </c>
       <c r="AV6" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日012 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8991,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>周日008</t>
+          <t>周日007</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -8623,17 +9001,17 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>国际赛</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>AC奥卢</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>雅罗</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -8651,39 +9029,15 @@
           <t>已接入实时赔率</t>
         </is>
       </c>
-      <c r="J23" s="8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="K23" s="8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="N23" s="8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="8" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
+      <c r="P23" s="8" t="inlineStr"/>
+      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="8" t="inlineStr"/>
       <c r="T23" s="8" t="inlineStr"/>
       <c r="U23" s="8" t="inlineStr"/>
@@ -8693,39 +9047,15 @@
       <c r="Y23" s="8" t="inlineStr"/>
       <c r="Z23" s="8" t="inlineStr"/>
       <c r="AA23" s="8" t="inlineStr"/>
-      <c r="AB23" s="8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC23" s="8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD23" s="8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE23" s="8" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AF23" s="8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG23" s="8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH23" s="8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AI23" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ23" s="8" t="inlineStr">
-        <is>
-          <t>+0.08</t>
-        </is>
-      </c>
+      <c r="AB23" s="8" t="inlineStr"/>
+      <c r="AC23" s="8" t="inlineStr"/>
+      <c r="AD23" s="8" t="inlineStr"/>
+      <c r="AE23" s="8" t="inlineStr"/>
+      <c r="AF23" s="8" t="inlineStr"/>
+      <c r="AG23" s="8" t="inlineStr"/>
+      <c r="AH23" s="8" t="inlineStr"/>
+      <c r="AI23" s="8" t="inlineStr"/>
+      <c r="AJ23" s="8" t="inlineStr"/>
       <c r="AK23" s="8" t="inlineStr">
         <is>
           <t>缺失</t>
@@ -8753,7 +9083,7 @@
       </c>
       <c r="AP23" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AQ23" s="8" t="inlineStr">
@@ -8777,11 +9107,11 @@
         </is>
       </c>
       <c r="AU23" s="8" t="n">
-        <v>57.36</v>
+        <v>59.77</v>
       </c>
       <c r="AV23" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬兰超级联赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -8793,7 +9123,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日008</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -8803,22 +9133,22 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>国际赛</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>AC奥卢</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>科索沃</t>
+          <t>雅罗</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31 22:00</t>
+          <t>2026-05-31 21:00</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -8832,36 +9162,36 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>5.2</v>
+        <v>4.35</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="R24" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="S24" s="9" t="inlineStr"/>
@@ -8874,36 +9204,36 @@
       <c r="Z24" s="9" t="inlineStr"/>
       <c r="AA24" s="9" t="inlineStr"/>
       <c r="AB24" s="9" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" s="9" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="AE24" s="9" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG24" s="9" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" s="9" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AI24" s="9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI24" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ24" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.08</t>
         </is>
       </c>
       <c r="AK24" s="9" t="inlineStr">
@@ -8933,7 +9263,7 @@
       </c>
       <c r="AP24" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="AQ24" s="9" t="inlineStr">
@@ -8957,11 +9287,11 @@
         </is>
       </c>
       <c r="AU24" s="9" t="n">
-        <v>54.23</v>
+        <v>57.36</v>
       </c>
       <c r="AV24" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬兰超级联赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -8973,7 +9303,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>周日011</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -8988,17 +9318,17 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>塞内加尔</t>
+          <t>科索沃</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>2026-06-01 03:30</t>
+          <t>2026-05-31 22:00</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -9012,22 +9342,22 @@
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2.43</v>
+        <v>1.51</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>2.43</v>
+        <v>1.51</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
@@ -9054,109 +9384,553 @@
       <c r="Z25" s="8" t="inlineStr"/>
       <c r="AA25" s="8" t="inlineStr"/>
       <c r="AB25" s="8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC25" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD25" s="8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AE25" s="8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF25" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG25" s="8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH25" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI25" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ25" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK25" s="8" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AL25" s="8" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AM25" s="8" t="inlineStr">
+        <is>
+          <t>500.com /jczq/ (Playwright)</t>
+        </is>
+      </c>
+      <c r="AN25" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="AO25" s="8" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="AP25" s="8" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="AQ25" s="8" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="AR25" s="8" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="AS25" s="8" t="inlineStr">
+        <is>
+          <t>平局-平局</t>
+        </is>
+      </c>
+      <c r="AT25" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AU25" s="8" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="AV25" s="8" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>周日010</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>芬兰</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:45</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31T12:15:15+08:00</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>已接入实时赔率</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
+      <c r="O26" s="9" t="inlineStr"/>
+      <c r="P26" s="9" t="inlineStr"/>
+      <c r="Q26" s="9" t="inlineStr"/>
+      <c r="R26" s="9" t="inlineStr"/>
+      <c r="S26" s="9" t="inlineStr"/>
+      <c r="T26" s="9" t="inlineStr"/>
+      <c r="U26" s="9" t="inlineStr"/>
+      <c r="V26" s="9" t="inlineStr"/>
+      <c r="W26" s="9" t="inlineStr"/>
+      <c r="X26" s="9" t="inlineStr"/>
+      <c r="Y26" s="9" t="inlineStr"/>
+      <c r="Z26" s="9" t="inlineStr"/>
+      <c r="AA26" s="9" t="inlineStr"/>
+      <c r="AB26" s="9" t="inlineStr"/>
+      <c r="AC26" s="9" t="inlineStr"/>
+      <c r="AD26" s="9" t="inlineStr"/>
+      <c r="AE26" s="9" t="inlineStr"/>
+      <c r="AF26" s="9" t="inlineStr"/>
+      <c r="AG26" s="9" t="inlineStr"/>
+      <c r="AH26" s="9" t="inlineStr"/>
+      <c r="AI26" s="9" t="inlineStr"/>
+      <c r="AJ26" s="9" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AL26" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AM26" s="9" t="inlineStr">
+        <is>
+          <t>500.com /jczq/ (Playwright)</t>
+        </is>
+      </c>
+      <c r="AN26" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="AO26" s="9" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="AP26" s="9" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="AQ26" s="9" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="AR26" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="AS26" s="9" t="inlineStr">
+        <is>
+          <t>平局-平局</t>
+        </is>
+      </c>
+      <c r="AT26" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AU26" s="9" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="AV26" s="9" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>周日011</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>塞内加尔</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 03:30</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31T12:15:15+08:00</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>已接入实时赔率</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr"/>
+      <c r="T27" s="8" t="inlineStr"/>
+      <c r="U27" s="8" t="inlineStr"/>
+      <c r="V27" s="8" t="inlineStr"/>
+      <c r="W27" s="8" t="inlineStr"/>
+      <c r="X27" s="8" t="inlineStr"/>
+      <c r="Y27" s="8" t="inlineStr"/>
+      <c r="Z27" s="8" t="inlineStr"/>
+      <c r="AA27" s="8" t="inlineStr"/>
+      <c r="AB27" s="8" t="n">
         <v>5.65</v>
       </c>
-      <c r="AC25" s="8" t="n">
+      <c r="AC27" s="8" t="n">
         <v>3.95</v>
       </c>
-      <c r="AD25" s="8" t="n">
+      <c r="AD27" s="8" t="n">
         <v>1.43</v>
       </c>
-      <c r="AE25" s="8" t="n">
+      <c r="AE27" s="8" t="n">
         <v>5.65</v>
       </c>
-      <c r="AF25" s="8" t="n">
+      <c r="AF27" s="8" t="n">
         <v>3.95</v>
       </c>
-      <c r="AG25" s="8" t="n">
+      <c r="AG27" s="8" t="n">
         <v>1.43</v>
       </c>
-      <c r="AH25" s="8" t="inlineStr">
+      <c r="AH27" s="8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI27" s="8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AJ25" s="8" t="inlineStr">
+      <c r="AJ27" s="8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK25" s="8" t="inlineStr">
+      <c r="AK27" s="8" t="inlineStr">
         <is>
           <t>缺失</t>
         </is>
       </c>
-      <c r="AL25" s="8" t="inlineStr">
+      <c r="AL27" s="8" t="inlineStr">
         <is>
           <t>缺失</t>
         </is>
       </c>
-      <c r="AM25" s="8" t="inlineStr">
+      <c r="AM27" s="8" t="inlineStr">
         <is>
           <t>500.com /jczq/ (Playwright)</t>
         </is>
       </c>
-      <c r="AN25" s="15" t="inlineStr">
+      <c r="AN27" s="15" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="AO25" s="8" t="inlineStr">
+      <c r="AO27" s="8" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="AP25" s="8" t="inlineStr">
+      <c r="AP27" s="8" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="AQ25" s="8" t="inlineStr">
+      <c r="AQ27" s="8" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="AR25" s="8" t="inlineStr">
+      <c r="AR27" s="8" t="inlineStr">
         <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="AS25" s="8" t="inlineStr">
+      <c r="AS27" s="8" t="inlineStr">
         <is>
           <t>客胜-客胜</t>
         </is>
       </c>
-      <c r="AT25" s="8" t="inlineStr">
+      <c r="AT27" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="AU25" s="8" t="n">
+      <c r="AU27" s="8" t="n">
         <v>8.98</v>
       </c>
-      <c r="AV25" s="8" t="inlineStr">
+      <c r="AV27" s="8" t="inlineStr">
         <is>
           <t>经模型综合分析：国际赛，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>巴拿马</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:30</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31T12:15:15+08:00</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>已接入实时赔率</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr"/>
+      <c r="N28" s="9" t="inlineStr"/>
+      <c r="O28" s="9" t="inlineStr"/>
+      <c r="P28" s="9" t="inlineStr"/>
+      <c r="Q28" s="9" t="inlineStr"/>
+      <c r="R28" s="9" t="inlineStr"/>
+      <c r="S28" s="9" t="inlineStr"/>
+      <c r="T28" s="9" t="inlineStr"/>
+      <c r="U28" s="9" t="inlineStr"/>
+      <c r="V28" s="9" t="inlineStr"/>
+      <c r="W28" s="9" t="inlineStr"/>
+      <c r="X28" s="9" t="inlineStr"/>
+      <c r="Y28" s="9" t="inlineStr"/>
+      <c r="Z28" s="9" t="inlineStr"/>
+      <c r="AA28" s="9" t="inlineStr"/>
+      <c r="AB28" s="9" t="inlineStr"/>
+      <c r="AC28" s="9" t="inlineStr"/>
+      <c r="AD28" s="9" t="inlineStr"/>
+      <c r="AE28" s="9" t="inlineStr"/>
+      <c r="AF28" s="9" t="inlineStr"/>
+      <c r="AG28" s="9" t="inlineStr"/>
+      <c r="AH28" s="9" t="inlineStr"/>
+      <c r="AI28" s="9" t="inlineStr"/>
+      <c r="AJ28" s="9" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AL28" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AM28" s="9" t="inlineStr">
+        <is>
+          <t>500.com /jczq/ (Playwright)</t>
+        </is>
+      </c>
+      <c r="AN28" s="15" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="AO28" s="9" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="AP28" s="9" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="AQ28" s="9" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="AR28" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="AS28" s="9" t="inlineStr">
+        <is>
+          <t>平局-平局</t>
+        </is>
+      </c>
+      <c r="AT28" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AU28" s="9" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="AV28" s="9" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AV27"/>
+  <autoFilter ref="A2:AV30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AV1"/>
-    <mergeCell ref="A27:AV27"/>
+    <mergeCell ref="A30:AV30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9168,7 +9942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9359,16 +10133,16 @@
         </is>
       </c>
       <c r="L3" s="8" t="n">
-        <v>97.58</v>
+        <v>59.77</v>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N3" s="8" t="inlineStr">
         <is>
-          <t>低｜主方向概率领先</t>
+          <t>高｜主方向概率领先</t>
         </is>
       </c>
       <c r="O3" s="8" t="inlineStr">
@@ -9398,7 +10172,7 @@
       </c>
       <c r="T3" s="11" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -9459,7 +10233,7 @@
         </is>
       </c>
       <c r="L4" s="9" t="n">
-        <v>95.84999999999999</v>
+        <v>59.79</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
@@ -9659,7 +10433,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>95.76000000000001</v>
+        <v>60.71</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -11310,7 +12084,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>周日008</t>
+          <t>周日007</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -11320,17 +12094,17 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>国际赛</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>AC奥卢</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>雅罗</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -11350,7 +12124,7 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -11359,7 +12133,7 @@
         </is>
       </c>
       <c r="L23" s="8" t="n">
-        <v>57.36</v>
+        <v>59.77</v>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
@@ -11373,7 +12147,7 @@
       </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
-          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.86</t>
+          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72</t>
         </is>
       </c>
       <c r="P23" s="8" t="inlineStr">
@@ -11393,12 +12167,12 @@
       </c>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化缺失</t>
+          <t>常规｜缺少初赔对比；亚盘变化缺失</t>
         </is>
       </c>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.86）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：缺少初赔对比（缺少初赔对比；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -11410,7 +12184,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日008</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -11420,22 +12194,22 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>国际赛</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>AC奥卢</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>科索沃</t>
+          <t>雅罗</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31 22:00</t>
+          <t>2026-05-31 21:00</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -11450,7 +12224,7 @@
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
@@ -11459,7 +12233,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>54.23</v>
+        <v>57.36</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
@@ -11473,7 +12247,7 @@
       </c>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72</t>
+          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.86</t>
         </is>
       </c>
       <c r="P24" s="9" t="inlineStr">
@@ -11498,7 +12272,7 @@
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.86）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -11510,110 +12284,410 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
+          <t>周日009</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>捷克</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>科索沃</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31 22:00</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>高｜主方向概率领先</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>推断｜杯赛/跨联赛战意以轮换和赛程优先</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>阵容缺口｜无阵容信息；伤停记录0条</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>缺口｜使用赔率与基础概率替代，信心需打折</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>常规｜赔率变化平稳；亚盘变化缺失</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>周日010</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>芬兰</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:45</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>高｜主方向概率领先</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72</t>
+        </is>
+      </c>
+      <c r="P26" s="9" t="inlineStr">
+        <is>
+          <t>推断｜杯赛/跨联赛战意以轮换和赛程优先</t>
+        </is>
+      </c>
+      <c r="Q26" s="9" t="inlineStr">
+        <is>
+          <t>阵容缺口｜无阵容信息；伤停记录0条</t>
+        </is>
+      </c>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>缺口｜使用赔率与基础概率替代，信心需打折</t>
+        </is>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>常规｜缺少初赔对比；亚盘变化缺失</t>
+        </is>
+      </c>
+      <c r="T26" s="14" t="inlineStr">
+        <is>
+          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：缺少初赔对比（缺少初赔对比；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>周日011</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>jingcai</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>国际赛</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>美国</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>塞内加尔</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>2026-06-01 03:30</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="L27" s="8" t="n">
         <v>8.98</v>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="N27" s="8" t="inlineStr">
         <is>
           <t>中高｜概率差过小</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
         <is>
           <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72</t>
         </is>
       </c>
-      <c r="P25" s="8" t="inlineStr">
+      <c r="P27" s="8" t="inlineStr">
         <is>
           <t>推断｜杯赛/跨联赛战意以轮换和赛程优先</t>
         </is>
       </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t>阵容缺口｜无阵容信息；伤停记录0条</t>
         </is>
       </c>
-      <c r="R25" s="8" t="inlineStr">
+      <c r="R27" s="8" t="inlineStr">
         <is>
           <t>缺口｜使用赔率与基础概率替代，信心需打折</t>
         </is>
       </c>
-      <c r="S25" s="8" t="inlineStr">
+      <c r="S27" s="8" t="inlineStr">
         <is>
           <t>常规｜赔率变化平稳；亚盘变化缺失</t>
         </is>
       </c>
-      <c r="T25" s="11" t="inlineStr">
+      <c r="T27" s="11" t="inlineStr">
         <is>
           <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>巴拿马</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:30</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t>高｜主方向概率领先</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72</t>
+        </is>
+      </c>
+      <c r="P28" s="9" t="inlineStr">
+        <is>
+          <t>推断｜杯赛/跨联赛战意以轮换和赛程优先</t>
+        </is>
+      </c>
+      <c r="Q28" s="9" t="inlineStr">
+        <is>
+          <t>阵容缺口｜无阵容信息；伤停记录0条</t>
+        </is>
+      </c>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>缺口｜使用赔率与基础概率替代，信心需打折</t>
+        </is>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>常规｜缺少初赔对比；亚盘变化缺失</t>
+        </is>
+      </c>
+      <c r="T28" s="14" t="inlineStr">
+        <is>
+          <t>主判断：主胜，防平局；冷门：高（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.72）；赔率：缺少初赔对比（缺少初赔对比；亚盘变化缺失）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T27"/>
+  <autoFilter ref="A2:T30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A27:T27"/>
+    <mergeCell ref="A30:T30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11625,7 +12699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11962,7 +13036,7 @@
       </c>
       <c r="AG3" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日007 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -12091,7 +13165,7 @@
       </c>
       <c r="AG4" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日010 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -12349,7 +13423,7 @@
       </c>
       <c r="AG6" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日012 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -14425,7 +15499,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>周日008</t>
+          <t>周日007</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -14435,17 +15509,17 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>国际赛</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>AC奥卢</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>雅罗</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -14468,21 +15542,21 @@
       <c r="P23" s="8" t="inlineStr"/>
       <c r="Q23" s="8" t="inlineStr"/>
       <c r="R23" s="8" t="n">
-        <v>2.855</v>
+        <v>2.718</v>
       </c>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="V23" s="8" t="inlineStr">
@@ -14492,7 +15566,7 @@
       </c>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>高压强攻/进球上限高</t>
+          <t>进攻优势/主动压制</t>
         </is>
       </c>
       <c r="X23" s="8" t="inlineStr">
@@ -14542,7 +15616,7 @@
       </c>
       <c r="AG23" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬兰超级联赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -14554,7 +15628,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日008</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -14564,22 +15638,22 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>国际赛</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>AC奥卢</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>科索沃</t>
+          <t>雅罗</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31 22:00</t>
+          <t>2026-05-31 21:00</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -14597,21 +15671,21 @@
       <c r="P24" s="9" t="inlineStr"/>
       <c r="Q24" s="9" t="inlineStr"/>
       <c r="R24" s="9" t="n">
-        <v>2.718</v>
+        <v>2.855</v>
       </c>
       <c r="S24" s="9" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="T24" s="9" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="U24" s="9" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="V24" s="9" t="inlineStr">
@@ -14621,7 +15695,7 @@
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>进攻优势/主动压制</t>
+          <t>高压强攻/进球上限高</t>
         </is>
       </c>
       <c r="X24" s="9" t="inlineStr">
@@ -14671,7 +15745,7 @@
       </c>
       <c r="AG24" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬兰超级联赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -14683,7 +15757,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>周日011</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -14698,17 +15772,17 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>塞内加尔</t>
+          <t>科索沃</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>2026-06-01 03:30</t>
+          <t>2026-05-31 22:00</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -14750,72 +15824,459 @@
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
+          <t>进攻优势/主动压制</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>防守承压/反击为主</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="Z25" s="8" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AA25" s="8" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AB25" s="8" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AC25" s="8" t="inlineStr">
+        <is>
+          <t>缺失/未返回</t>
+        </is>
+      </c>
+      <c r="AD25" s="8" t="inlineStr">
+        <is>
+          <t>缺失：未配置/未返回 LINEUP_SOURCE_URL</t>
+        </is>
+      </c>
+      <c r="AE25" s="8" t="inlineStr">
+        <is>
+          <t>未公布/未返回；通常赛前约1小时才有</t>
+        </is>
+      </c>
+      <c r="AF25" s="8" t="inlineStr">
+        <is>
+          <t>缺 LINEUP_SOURCE_URL/API-Football 未匹配</t>
+        </is>
+      </c>
+      <c r="AG25" s="8" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>周日010</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>芬兰</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:45</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>未抓到大小球盘口，使用模型派生</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
+      <c r="O26" s="9" t="inlineStr"/>
+      <c r="P26" s="9" t="inlineStr"/>
+      <c r="Q26" s="9" t="inlineStr"/>
+      <c r="R26" s="9" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>51.1%</t>
+        </is>
+      </c>
+      <c r="T26" s="9" t="inlineStr">
+        <is>
+          <t>48.9%</t>
+        </is>
+      </c>
+      <c r="U26" s="9" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="V26" s="9" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>进攻优势/主动压制</t>
+        </is>
+      </c>
+      <c r="X26" s="9" t="inlineStr">
+        <is>
+          <t>防守承压/反击为主</t>
+        </is>
+      </c>
+      <c r="Y26" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="Z26" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AA26" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AB26" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AC26" s="9" t="inlineStr">
+        <is>
+          <t>缺失/未返回</t>
+        </is>
+      </c>
+      <c r="AD26" s="9" t="inlineStr">
+        <is>
+          <t>缺失：未配置/未返回 LINEUP_SOURCE_URL</t>
+        </is>
+      </c>
+      <c r="AE26" s="9" t="inlineStr">
+        <is>
+          <t>未公布/未返回；通常赛前约1小时才有</t>
+        </is>
+      </c>
+      <c r="AF26" s="9" t="inlineStr">
+        <is>
+          <t>缺 LINEUP_SOURCE_URL/API-Football 未匹配</t>
+        </is>
+      </c>
+      <c r="AG26" s="9" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>周日011</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>塞内加尔</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01 03:30</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>未抓到大小球盘口，使用模型派生</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="8" t="inlineStr"/>
+      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="R27" s="8" t="n">
+        <v>2.718</v>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>51.1%</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>48.9%</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
           <t>均衡偏主动</t>
         </is>
       </c>
-      <c r="X25" s="8" t="inlineStr">
+      <c r="X27" s="8" t="inlineStr">
         <is>
           <t>均衡偏主动</t>
         </is>
       </c>
-      <c r="Y25" s="8" t="inlineStr">
+      <c r="Y27" s="8" t="inlineStr">
         <is>
           <t>缺失</t>
         </is>
       </c>
-      <c r="Z25" s="8" t="inlineStr">
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>缺失</t>
         </is>
       </c>
-      <c r="AA25" s="8" t="inlineStr">
+      <c r="AA27" s="8" t="inlineStr">
         <is>
           <t>缺失</t>
         </is>
       </c>
-      <c r="AB25" s="8" t="inlineStr">
+      <c r="AB27" s="8" t="inlineStr">
         <is>
           <t>缺失</t>
         </is>
       </c>
-      <c r="AC25" s="8" t="inlineStr">
+      <c r="AC27" s="8" t="inlineStr">
         <is>
           <t>缺失/未返回</t>
         </is>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
+      <c r="AD27" s="8" t="inlineStr">
         <is>
           <t>缺失：未配置/未返回 LINEUP_SOURCE_URL</t>
         </is>
       </c>
-      <c r="AE25" s="8" t="inlineStr">
+      <c r="AE27" s="8" t="inlineStr">
         <is>
           <t>未公布/未返回；通常赛前约1小时才有</t>
         </is>
       </c>
-      <c r="AF25" s="8" t="inlineStr">
+      <c r="AF27" s="8" t="inlineStr">
         <is>
           <t>缺 LINEUP_SOURCE_URL/API-Football 未匹配</t>
         </is>
       </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="AG27" s="8" t="inlineStr">
         <is>
           <t>经模型综合分析：国际赛，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>jingcai</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>巴拿马</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:30</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>未抓到大小球盘口，使用模型派生</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr"/>
+      <c r="N28" s="9" t="inlineStr"/>
+      <c r="O28" s="9" t="inlineStr"/>
+      <c r="P28" s="9" t="inlineStr"/>
+      <c r="Q28" s="9" t="inlineStr"/>
+      <c r="R28" s="9" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>51.1%</t>
+        </is>
+      </c>
+      <c r="T28" s="9" t="inlineStr">
+        <is>
+          <t>48.9%</t>
+        </is>
+      </c>
+      <c r="U28" s="9" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="V28" s="9" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>进攻优势/主动压制</t>
+        </is>
+      </c>
+      <c r="X28" s="9" t="inlineStr">
+        <is>
+          <t>防守承压/反击为主</t>
+        </is>
+      </c>
+      <c r="Y28" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="Z28" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AA28" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AB28" s="9" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="AC28" s="9" t="inlineStr">
+        <is>
+          <t>缺失/未返回</t>
+        </is>
+      </c>
+      <c r="AD28" s="9" t="inlineStr">
+        <is>
+          <t>缺失：未配置/未返回 LINEUP_SOURCE_URL</t>
+        </is>
+      </c>
+      <c r="AE28" s="9" t="inlineStr">
+        <is>
+          <t>未公布/未返回；通常赛前约1小时才有</t>
+        </is>
+      </c>
+      <c r="AF28" s="9" t="inlineStr">
+        <is>
+          <t>缺 LINEUP_SOURCE_URL/API-Football 未匹配</t>
+        </is>
+      </c>
+      <c r="AG28" s="9" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AG27"/>
+  <autoFilter ref="A2:AG30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A27:AG27"/>
+    <mergeCell ref="A30:AG30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14827,7 +16288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15069,7 +16530,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -15083,13 +16544,13 @@
         </is>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0.764</v>
+        <v>0.6695</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.1821</v>
+        <v>0.2571</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.0539</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>0.7876</v>
@@ -15116,11 +16577,11 @@
       </c>
       <c r="U3" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V3" s="8" t="n">
-        <v>97.58</v>
+        <v>59.77</v>
       </c>
       <c r="W3" s="8" t="inlineStr">
         <is>
@@ -15152,7 +16613,7 @@
       </c>
       <c r="AE3" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日007 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AF3" s="8" t="n">
@@ -15208,7 +16669,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -15222,13 +16683,13 @@
         </is>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.669</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>0.1811</v>
+        <v>0.256</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>0.0553</v>
+        <v>0.075</v>
       </c>
       <c r="N4" s="9" t="n">
         <v>0.8398</v>
@@ -15259,7 +16720,7 @@
         </is>
       </c>
       <c r="V4" s="9" t="n">
-        <v>95.84999999999999</v>
+        <v>59.79</v>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -15291,7 +16752,7 @@
       </c>
       <c r="AE4" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日010 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AF4" s="9" t="n">
@@ -15486,7 +16947,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -15500,13 +16961,13 @@
         </is>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.765</v>
+        <v>0.6754</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.1847</v>
+        <v>0.2573</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.0503</v>
+        <v>0.0673</v>
       </c>
       <c r="N6" s="9" t="n">
         <v>0.8421</v>
@@ -15537,7 +16998,7 @@
         </is>
       </c>
       <c r="V6" s="9" t="n">
-        <v>95.76000000000001</v>
+        <v>60.71</v>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -15569,7 +17030,7 @@
       </c>
       <c r="AE6" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周日012 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AF6" s="9" t="n">
@@ -17819,17 +19280,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>周日008</t>
+          <t>周日007</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>国际赛</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>AC奥卢 对 雅罗</t>
+          <t>瑞士 对 约旦</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -17844,7 +19305,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -17863,35 +19324,35 @@
         </is>
       </c>
       <c r="K23" s="8" t="n">
-        <v>0.5793</v>
+        <v>0.6695</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.2304</v>
+        <v>0.2571</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.1903</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>0.5747</v>
+        <v>0.764</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>0.2329</v>
+        <v>0.1821</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>0.1924</v>
+        <v>0.0539</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>0.702</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>0.1858</v>
+        <v>0.2109</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>0.1123</v>
+        <v>0.1506</v>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:12.3% / 3-0:9.3%</t>
+          <t>1-0:12.5% / 2-0:12.1% / 2-1:10.2%</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -17900,47 +19361,39 @@
         </is>
       </c>
       <c r="V23" s="8" t="n">
-        <v>57.36</v>
+        <v>59.77</v>
       </c>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>🟡 可选</t>
+          <t>🟢 建议下注</t>
         </is>
       </c>
       <c r="X23" s="8" t="inlineStr">
         <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="n">
-        <v>-0.1079</v>
-      </c>
-      <c r="Z23" s="8" t="n">
-        <v>0</v>
-      </c>
+          <t>跳过</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr"/>
+      <c r="Z23" s="8" t="inlineStr"/>
       <c r="AA23" s="8" t="n">
-        <v>0.4814</v>
+        <v>0.4248</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>0.2223</v>
+        <v>0.2159</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>0.2963</v>
+        <v>0.3593</v>
       </c>
       <c r="AD23" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE23" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬兰超级联赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG23" s="8" t="n">
-        <v>1.59</v>
-      </c>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr"/>
+      <c r="AG23" s="8" t="inlineStr"/>
       <c r="AH23" s="8" t="inlineStr">
         <is>
           <t>2026-05-31T12:15:15+08:00</t>
@@ -17958,17 +19411,17 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>周日009</t>
+          <t>周日008</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>国际赛</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>捷克 对 科索沃</t>
+          <t>AC奥卢 对 雅罗</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -17983,7 +19436,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -18002,35 +19455,35 @@
         </is>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.5735</v>
+        <v>0.5793</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.2547</v>
+        <v>0.2304</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>0.1718</v>
+        <v>0.1903</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>0.5868</v>
+        <v>0.5747</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>0.2428</v>
+        <v>0.2329</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0.1704</v>
+        <v>0.1924</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>0.5707</v>
+        <v>0.702</v>
       </c>
       <c r="R24" s="9" t="n">
-        <v>0.2328</v>
+        <v>0.1858</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>0.1966</v>
+        <v>0.1123</v>
       </c>
       <c r="T24" s="9" t="inlineStr">
         <is>
-          <t>1-0:11.6% / 1-1:10.9% / 2-0:10.7%</t>
+          <t>2-0:13.5% / 1-0:12.3% / 3-0:9.3%</t>
         </is>
       </c>
       <c r="U24" s="9" t="inlineStr">
@@ -18039,7 +19492,7 @@
         </is>
       </c>
       <c r="V24" s="9" t="n">
-        <v>54.23</v>
+        <v>57.36</v>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -18052,33 +19505,33 @@
         </is>
       </c>
       <c r="Y24" s="9" t="n">
-        <v>-0.134</v>
+        <v>-0.1079</v>
       </c>
       <c r="Z24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AA24" s="9" t="n">
-        <v>0.4859</v>
+        <v>0.4814</v>
       </c>
       <c r="AB24" s="9" t="n">
-        <v>0.226</v>
+        <v>0.2223</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>0.2881</v>
+        <v>0.2963</v>
       </c>
       <c r="AD24" s="9" t="n">
         <v>4</v>
       </c>
       <c r="AE24" s="9" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬兰超级联赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AG24" s="9" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AH24" s="9" t="inlineStr">
         <is>
@@ -18097,7 +19550,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>周日011</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -18107,7 +19560,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>美国 对 塞内加尔</t>
+          <t>捷克 对 科索沃</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -18117,7 +19570,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -18127,7 +19580,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -18137,39 +19590,39 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K25" s="8" t="n">
-        <v>0.3592</v>
+        <v>0.5735</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.2886</v>
+        <v>0.2547</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.3523</v>
+        <v>0.1718</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>0.3643</v>
+        <v>0.5868</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>0.2951</v>
+        <v>0.2428</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>0.3405</v>
+        <v>0.1704</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>0.4389</v>
+        <v>0.5707</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>0.2555</v>
+        <v>0.2328</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>0.3057</v>
+        <v>0.1966</v>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:9.6% / 2-1:8.9%</t>
+          <t>1-0:11.6% / 1-1:10.9% / 2-0:10.7%</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
@@ -18178,11 +19631,11 @@
         </is>
       </c>
       <c r="V25" s="8" t="n">
-        <v>8.98</v>
+        <v>54.23</v>
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>⚪ 慎选/观望</t>
+          <t>🟡 可选</t>
         </is>
       </c>
       <c r="X25" s="8" t="inlineStr">
@@ -18191,33 +19644,33 @@
         </is>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>-0.1271</v>
+        <v>-0.134</v>
       </c>
       <c r="Z25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AA25" s="8" t="n">
-        <v>0.402</v>
+        <v>0.4859</v>
       </c>
       <c r="AB25" s="8" t="n">
-        <v>0.2458</v>
+        <v>0.226</v>
       </c>
       <c r="AC25" s="8" t="n">
-        <v>0.3522</v>
+        <v>0.2881</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>4</v>
       </c>
       <c r="AE25" s="8" t="inlineStr">
         <is>
-          <t>经模型综合分析：国际赛，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AF25" s="8" t="n">
-        <v>2.43</v>
+        <v>1.51</v>
       </c>
       <c r="AG25" s="8" t="n">
-        <v>2.43</v>
+        <v>1.51</v>
       </c>
       <c r="AH25" s="8" t="inlineStr">
         <is>
@@ -18228,18 +19681,419 @@
       <c r="AJ25" s="8" t="inlineStr"/>
       <c r="AK25" s="8" t="inlineStr"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>周日010</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>德国 对 芬兰</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>平局-平局</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>0.7635999999999999</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="R26" s="9" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="T26" s="9" t="inlineStr">
+        <is>
+          <t>1-0:12.3% / 2-0:11.5% / 1-1:10%</t>
+        </is>
+      </c>
+      <c r="U26" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="V26" s="9" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>🟢 建议下注</t>
+        </is>
+      </c>
+      <c r="X26" s="9" t="inlineStr">
+        <is>
+          <t>跳过</t>
+        </is>
+      </c>
+      <c r="Y26" s="9" t="inlineStr"/>
+      <c r="Z26" s="9" t="inlineStr"/>
+      <c r="AA26" s="9" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="AB26" s="9" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="AC26" s="9" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AD26" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" s="9" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+      <c r="AF26" s="9" t="inlineStr"/>
+      <c r="AG26" s="9" t="inlineStr"/>
+      <c r="AH26" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31T12:15:15+08:00</t>
+        </is>
+      </c>
+      <c r="AI26" s="9" t="inlineStr"/>
+      <c r="AJ26" s="9" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>周日011</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>美国 对 塞内加尔</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>1-1:12.2% / 1-0:9.6% / 2-1:8.9%</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 慎选/观望</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t>观察/跳过</t>
+        </is>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>-0.1271</v>
+      </c>
+      <c r="Z27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="8" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="AB27" s="8" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="AC27" s="8" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="AD27" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" s="8" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+      <c r="AF27" s="8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG27" s="8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH27" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-31T12:15:15+08:00</t>
+        </is>
+      </c>
+      <c r="AI27" s="8" t="inlineStr"/>
+      <c r="AJ27" s="8" t="inlineStr"/>
+      <c r="AK27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>周日012</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>国际赛</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>巴西 对 巴拿马</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>平局-平局</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="N28" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="P28" s="9" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>0.6346000000000001</v>
+      </c>
+      <c r="R28" s="9" t="n">
+        <v>0.2155</v>
+      </c>
+      <c r="S28" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T28" s="9" t="inlineStr">
+        <is>
+          <t>1-0:12.7% / 2-0:11.8% / 1-1:10.4%</t>
+        </is>
+      </c>
+      <c r="U28" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="V28" s="9" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>🟢 建议下注</t>
+        </is>
+      </c>
+      <c r="X28" s="9" t="inlineStr">
+        <is>
+          <t>跳过</t>
+        </is>
+      </c>
+      <c r="Y28" s="9" t="inlineStr"/>
+      <c r="Z28" s="9" t="inlineStr"/>
+      <c r="AA28" s="9" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="AB28" s="9" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="AC28" s="9" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AD28" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE28" s="9" t="inlineStr">
+        <is>
+          <t>经模型综合分析：国际赛，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+        </is>
+      </c>
+      <c r="AF28" s="9" t="inlineStr"/>
+      <c r="AG28" s="9" t="inlineStr"/>
+      <c r="AH28" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31T12:15:15+08:00</t>
+        </is>
+      </c>
+      <c r="AI28" s="9" t="inlineStr"/>
+      <c r="AJ28" s="9" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>⚡ Claude 神选 · 独立大模型 · 自主推断 · 2026-05-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AK27"/>
+  <autoFilter ref="A2:AK30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A27:AK27"/>
+    <mergeCell ref="A30:AK30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
